--- a/research/traditional_assets/database/data/nigeria/nigeria_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_retail_automotive.xlsx
@@ -1263,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1400,22 +1400,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1477375342772466</v>
+        <v>0.1473258216744148</v>
       </c>
       <c r="C2">
-        <v>11.30121436459657</v>
+        <v>11.24600694148875</v>
       </c>
       <c r="D2">
-        <v>11.14421436459657</v>
+        <v>11.18940694148876</v>
       </c>
       <c r="E2">
-        <v>-8.130000000000001</v>
+        <v>-8.0296</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1004</v>
       </c>
       <c r="G2">
         <v>0.157</v>
@@ -1436,28 +1436,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.005050120000000001</v>
       </c>
       <c r="N2">
-        <v>1.200333333333333</v>
+        <v>1.195283213333333</v>
       </c>
       <c r="O2">
-        <v>0.3601</v>
+        <v>0.358584964</v>
       </c>
       <c r="P2">
-        <v>0.8402333333333333</v>
+        <v>0.8366982493333333</v>
       </c>
       <c r="Q2">
-        <v>0.8882333333333333</v>
+        <v>0.8846982493333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1477375342772466</v>
+        <v>0.1484583047216312</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.715779132449463</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>237.6841210373879</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1482,22 +1482,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1473258216744148</v>
+        <v>0.1469141090715831</v>
       </c>
       <c r="C3">
-        <v>11.24600694148875</v>
+        <v>11.19116754522964</v>
       </c>
       <c r="D3">
-        <v>11.18940694148876</v>
+        <v>11.23496754522964</v>
       </c>
       <c r="E3">
-        <v>-8.0296</v>
+        <v>-7.929200000000001</v>
       </c>
       <c r="F3">
-        <v>0.1004</v>
+        <v>0.2008</v>
       </c>
       <c r="G3">
         <v>0.157</v>
@@ -1518,28 +1518,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M3">
-        <v>0.005050120000000001</v>
+        <v>0.01010024</v>
       </c>
       <c r="N3">
-        <v>1.195283213333333</v>
+        <v>1.190233093333333</v>
       </c>
       <c r="O3">
-        <v>0.358584964</v>
+        <v>0.3570699279999999</v>
       </c>
       <c r="P3">
-        <v>0.8366982493333333</v>
+        <v>0.8331631653333332</v>
       </c>
       <c r="Q3">
-        <v>0.8846982493333333</v>
+        <v>0.8811631653333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1484583047216312</v>
+        <v>0.1491937847669216</v>
       </c>
       <c r="T3">
-        <v>0.715779132449463</v>
+        <v>0.7209072248154859</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>237.6841210373879</v>
+        <v>118.8420605186939</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1564,22 +1564,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1469141090715831</v>
+        <v>0.1465023964687514</v>
       </c>
       <c r="C4">
-        <v>11.19116754522964</v>
+        <v>11.1367006897523</v>
       </c>
       <c r="D4">
-        <v>11.23496754522964</v>
+        <v>11.2809006897523</v>
       </c>
       <c r="E4">
-        <v>-7.929200000000001</v>
+        <v>-7.828800000000001</v>
       </c>
       <c r="F4">
-        <v>0.2008</v>
+        <v>0.3012</v>
       </c>
       <c r="G4">
         <v>0.157</v>
@@ -1600,28 +1600,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M4">
-        <v>0.01010024</v>
+        <v>0.01515036</v>
       </c>
       <c r="N4">
-        <v>1.190233093333333</v>
+        <v>1.185182973333333</v>
       </c>
       <c r="O4">
-        <v>0.3570699279999999</v>
+        <v>0.355554892</v>
       </c>
       <c r="P4">
-        <v>0.8331631653333332</v>
+        <v>0.8296280813333332</v>
       </c>
       <c r="Q4">
-        <v>0.8811631653333333</v>
+        <v>0.8776280813333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1491937847669216</v>
+        <v>0.1499444293492282</v>
       </c>
       <c r="T4">
-        <v>0.7209072248154859</v>
+        <v>0.7261410510447256</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>118.8420605186939</v>
+        <v>79.22804034579596</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1465023964687514</v>
+        <v>0.1460906838659196</v>
       </c>
       <c r="C5">
-        <v>11.1367006897523</v>
+        <v>11.08261096311202</v>
       </c>
       <c r="D5">
-        <v>11.2809006897523</v>
+        <v>11.32721096311202</v>
       </c>
       <c r="E5">
-        <v>-7.828800000000001</v>
+        <v>-7.728400000000001</v>
       </c>
       <c r="F5">
-        <v>0.3012</v>
+        <v>0.4016000000000001</v>
       </c>
       <c r="G5">
         <v>0.157</v>
@@ -1682,28 +1682,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M5">
-        <v>0.01515036</v>
+        <v>0.02020048</v>
       </c>
       <c r="N5">
-        <v>1.185182973333333</v>
+        <v>1.180132853333333</v>
       </c>
       <c r="O5">
-        <v>0.355554892</v>
+        <v>0.354039856</v>
       </c>
       <c r="P5">
-        <v>0.8296280813333332</v>
+        <v>0.8260929973333333</v>
       </c>
       <c r="Q5">
-        <v>0.8776280813333333</v>
+        <v>0.8740929973333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1499444293492282</v>
+        <v>0.150710712360333</v>
       </c>
       <c r="T5">
-        <v>0.7261410510447256</v>
+        <v>0.7314839153204079</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>79.22804034579596</v>
+        <v>59.42103025934696</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1728,22 +1728,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1460906838659196</v>
+        <v>0.1456789712630879</v>
       </c>
       <c r="C6">
-        <v>11.08261096311202</v>
+        <v>11.02890302901409</v>
       </c>
       <c r="D6">
-        <v>11.32721096311202</v>
+        <v>11.37390302901409</v>
       </c>
       <c r="E6">
-        <v>-7.728400000000001</v>
+        <v>-7.628000000000001</v>
       </c>
       <c r="F6">
-        <v>0.4016000000000001</v>
+        <v>0.5020000000000001</v>
       </c>
       <c r="G6">
         <v>0.157</v>
@@ -1764,28 +1764,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M6">
-        <v>0.02020048</v>
+        <v>0.0252506</v>
       </c>
       <c r="N6">
-        <v>1.180132853333333</v>
+        <v>1.175082733333333</v>
       </c>
       <c r="O6">
-        <v>0.354039856</v>
+        <v>0.35252482</v>
       </c>
       <c r="P6">
-        <v>0.8260929973333333</v>
+        <v>0.8225579133333334</v>
       </c>
       <c r="Q6">
-        <v>0.8740929973333333</v>
+        <v>0.8705579133333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.150710712360333</v>
+        <v>0.1514931276453557</v>
       </c>
       <c r="T6">
-        <v>0.7314839153204079</v>
+        <v>0.7369392609492624</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>59.42103025934696</v>
+        <v>47.53682420747757</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1810,22 +1810,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1456789712630879</v>
+        <v>0.1452672586602561</v>
       </c>
       <c r="C7">
-        <v>11.02890302901409</v>
+        <v>10.9755816283794</v>
       </c>
       <c r="D7">
-        <v>11.37390302901409</v>
+        <v>11.4209816283794</v>
       </c>
       <c r="E7">
-        <v>-7.628000000000001</v>
+        <v>-7.527600000000001</v>
       </c>
       <c r="F7">
-        <v>0.5020000000000001</v>
+        <v>0.6024000000000002</v>
       </c>
       <c r="G7">
         <v>0.157</v>
@@ -1846,28 +1846,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M7">
-        <v>0.0252506</v>
+        <v>0.03030072000000001</v>
       </c>
       <c r="N7">
-        <v>1.175082733333333</v>
+        <v>1.170032613333333</v>
       </c>
       <c r="O7">
-        <v>0.35252482</v>
+        <v>0.3510097839999999</v>
       </c>
       <c r="P7">
-        <v>0.8225579133333334</v>
+        <v>0.8190228293333333</v>
       </c>
       <c r="Q7">
-        <v>0.8705579133333334</v>
+        <v>0.8670228293333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1514931276453557</v>
+        <v>0.1522921900641023</v>
       </c>
       <c r="T7">
-        <v>0.7369392609492624</v>
+        <v>0.7425106777617095</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>47.53682420747757</v>
+        <v>39.61402017289797</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1892,22 +1892,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1452672586602561</v>
+        <v>0.1448555460574244</v>
       </c>
       <c r="C8">
-        <v>10.9755816283794</v>
+        <v>10.92265158094911</v>
       </c>
       <c r="D8">
-        <v>11.4209816283794</v>
+        <v>11.46845158094911</v>
       </c>
       <c r="E8">
-        <v>-7.527600000000001</v>
+        <v>-7.427200000000001</v>
       </c>
       <c r="F8">
-        <v>0.6024</v>
+        <v>0.7028</v>
       </c>
       <c r="G8">
         <v>0.157</v>
@@ -1928,28 +1928,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M8">
-        <v>0.03030072</v>
+        <v>0.03535083999999999</v>
       </c>
       <c r="N8">
-        <v>1.170032613333333</v>
+        <v>1.164982493333333</v>
       </c>
       <c r="O8">
-        <v>0.3510097839999999</v>
+        <v>0.349494748</v>
       </c>
       <c r="P8">
-        <v>0.8190228293333333</v>
+        <v>0.8154877453333333</v>
       </c>
       <c r="Q8">
-        <v>0.8670228293333333</v>
+        <v>0.8634877453333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1522921900641023</v>
+        <v>0.1531084366208865</v>
       </c>
       <c r="T8">
-        <v>0.7425106777617095</v>
+        <v>0.7482019099894783</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>39.61402017289798</v>
+        <v>33.95487443391256</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1974,22 +1974,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1448555460574244</v>
+        <v>0.1444438334545927</v>
       </c>
       <c r="C9">
-        <v>10.92265158094911</v>
+        <v>10.87011778692959</v>
       </c>
       <c r="D9">
-        <v>11.46845158094911</v>
+        <v>11.51631778692959</v>
       </c>
       <c r="E9">
-        <v>-7.427200000000001</v>
+        <v>-7.3268</v>
       </c>
       <c r="F9">
-        <v>0.7028000000000001</v>
+        <v>0.8032000000000001</v>
       </c>
       <c r="G9">
         <v>0.157</v>
@@ -2010,28 +2010,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M9">
-        <v>0.03535084</v>
+        <v>0.04040096000000001</v>
       </c>
       <c r="N9">
-        <v>1.164982493333333</v>
+        <v>1.159932373333333</v>
       </c>
       <c r="O9">
-        <v>0.349494748</v>
+        <v>0.347979712</v>
       </c>
       <c r="P9">
-        <v>0.8154877453333333</v>
+        <v>0.8119526613333333</v>
       </c>
       <c r="Q9">
-        <v>0.8634877453333334</v>
+        <v>0.8599526613333334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1531084366208865</v>
+        <v>0.1539424276680355</v>
       </c>
       <c r="T9">
-        <v>0.7482019099894783</v>
+        <v>0.754016864656981</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.95487443391255</v>
+        <v>29.71051512967348</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2056,22 +2056,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1444438334545927</v>
+        <v>0.1440321208517609</v>
       </c>
       <c r="C10">
-        <v>10.87011778692959</v>
+        <v>10.81798522867861</v>
       </c>
       <c r="D10">
-        <v>11.51631778692959</v>
+        <v>11.56458522867861</v>
       </c>
       <c r="E10">
-        <v>-7.3268</v>
+        <v>-7.226400000000001</v>
       </c>
       <c r="F10">
-        <v>0.8032000000000001</v>
+        <v>0.9036000000000001</v>
       </c>
       <c r="G10">
         <v>0.157</v>
@@ -2092,28 +2092,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M10">
-        <v>0.04040096000000001</v>
+        <v>0.04545108</v>
       </c>
       <c r="N10">
-        <v>1.159932373333333</v>
+        <v>1.154882253333333</v>
       </c>
       <c r="O10">
-        <v>0.347979712</v>
+        <v>0.3464646759999999</v>
       </c>
       <c r="P10">
-        <v>0.8119526613333333</v>
+        <v>0.8084175773333333</v>
       </c>
       <c r="Q10">
-        <v>0.8599526613333334</v>
+        <v>0.8564175773333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1539424276680355</v>
+        <v>0.1547947481887483</v>
       </c>
       <c r="T10">
-        <v>0.754016864656981</v>
+        <v>0.7599596205259672</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.71051512967348</v>
+        <v>26.40934678193199</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2138,22 +2138,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1440321208517609</v>
+        <v>0.1436204082489292</v>
       </c>
       <c r="C11">
-        <v>10.81798522867861</v>
+        <v>10.76625897243413</v>
       </c>
       <c r="D11">
-        <v>11.56458522867861</v>
+        <v>11.61325897243413</v>
       </c>
       <c r="E11">
-        <v>-7.226400000000001</v>
+        <v>-7.126000000000001</v>
       </c>
       <c r="F11">
-        <v>0.9036000000000001</v>
+        <v>1.004</v>
       </c>
       <c r="G11">
         <v>0.157</v>
@@ -2174,28 +2174,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M11">
-        <v>0.04545108</v>
+        <v>0.0505012</v>
       </c>
       <c r="N11">
-        <v>1.154882253333333</v>
+        <v>1.149832133333333</v>
       </c>
       <c r="O11">
-        <v>0.3464646759999999</v>
+        <v>0.3449496399999999</v>
       </c>
       <c r="P11">
-        <v>0.8084175773333333</v>
+        <v>0.8048824933333333</v>
       </c>
       <c r="Q11">
-        <v>0.8564175773333333</v>
+        <v>0.8528824933333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1547947481887483</v>
+        <v>0.1556660091654769</v>
       </c>
       <c r="T11">
-        <v>0.7599596205259672</v>
+        <v>0.7660344376364866</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.40934678193199</v>
+        <v>23.76841210373879</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2220,22 +2220,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1436204082489292</v>
+        <v>0.1432086956460975</v>
       </c>
       <c r="C12">
-        <v>10.76625897243413</v>
+        <v>10.71494417008703</v>
       </c>
       <c r="D12">
-        <v>11.61325897243413</v>
+        <v>11.66234417008703</v>
       </c>
       <c r="E12">
-        <v>-7.126</v>
+        <v>-7.025600000000001</v>
       </c>
       <c r="F12">
-        <v>1.004</v>
+        <v>1.1044</v>
       </c>
       <c r="G12">
         <v>0.157</v>
@@ -2256,28 +2256,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M12">
-        <v>0.05050120000000001</v>
+        <v>0.05555132</v>
       </c>
       <c r="N12">
-        <v>1.149832133333333</v>
+        <v>1.144782013333333</v>
       </c>
       <c r="O12">
-        <v>0.3449496399999999</v>
+        <v>0.343434604</v>
       </c>
       <c r="P12">
-        <v>0.8048824933333333</v>
+        <v>0.8013474093333333</v>
       </c>
       <c r="Q12">
-        <v>0.8528824933333333</v>
+        <v>0.8493474093333333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1556660091654769</v>
+        <v>0.1565568490405589</v>
       </c>
       <c r="T12">
-        <v>0.7660344376364866</v>
+        <v>0.7722457674910626</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.76841210373878</v>
+        <v>21.60764736703526</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2302,22 +2302,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1432086956460975</v>
+        <v>0.1427969830432657</v>
       </c>
       <c r="C13">
-        <v>10.71494417008703</v>
+        <v>10.66404606099888</v>
       </c>
       <c r="D13">
-        <v>11.66234417008703</v>
+        <v>11.71184606099888</v>
       </c>
       <c r="E13">
-        <v>-7.025600000000001</v>
+        <v>-6.9252</v>
       </c>
       <c r="F13">
-        <v>1.1044</v>
+        <v>1.2048</v>
       </c>
       <c r="G13">
         <v>0.157</v>
@@ -2338,28 +2338,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M13">
-        <v>0.05555132</v>
+        <v>0.06060144</v>
       </c>
       <c r="N13">
-        <v>1.144782013333333</v>
+        <v>1.139731893333333</v>
       </c>
       <c r="O13">
-        <v>0.343434604</v>
+        <v>0.341919568</v>
       </c>
       <c r="P13">
-        <v>0.8013474093333333</v>
+        <v>0.7978123253333333</v>
       </c>
       <c r="Q13">
-        <v>0.8493474093333333</v>
+        <v>0.8458123253333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1565568490405589</v>
+        <v>0.1574679352764383</v>
       </c>
       <c r="T13">
-        <v>0.7722457674910626</v>
+        <v>0.7785982639332425</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.60764736703526</v>
+        <v>19.80701008644899</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2384,22 +2384,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1427969830432657</v>
+        <v>0.142385270440434</v>
       </c>
       <c r="C14">
-        <v>10.66404606099888</v>
+        <v>10.61356997386624</v>
       </c>
       <c r="D14">
-        <v>11.71184606099888</v>
+        <v>11.76176997386624</v>
       </c>
       <c r="E14">
-        <v>-6.9252</v>
+        <v>-6.824800000000001</v>
       </c>
       <c r="F14">
-        <v>1.2048</v>
+        <v>1.3052</v>
       </c>
       <c r="G14">
         <v>0.157</v>
@@ -2420,28 +2420,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M14">
-        <v>0.06060144</v>
+        <v>0.06565156</v>
       </c>
       <c r="N14">
-        <v>1.139731893333333</v>
+        <v>1.134681773333333</v>
       </c>
       <c r="O14">
-        <v>0.341919568</v>
+        <v>0.3404045319999999</v>
       </c>
       <c r="P14">
-        <v>0.7978123253333333</v>
+        <v>0.7942772413333332</v>
       </c>
       <c r="Q14">
-        <v>0.8458123253333334</v>
+        <v>0.8422772413333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1574679352764383</v>
+        <v>0.1583999660234873</v>
       </c>
       <c r="T14">
-        <v>0.7785982639332425</v>
+        <v>0.785096794776392</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.80701008644899</v>
+        <v>18.28339392595291</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2466,22 +2466,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.142385270440434</v>
+        <v>0.1419735578376022</v>
       </c>
       <c r="C15">
-        <v>10.61356997386624</v>
+        <v>10.56352132863285</v>
       </c>
       <c r="D15">
-        <v>11.76176997386624</v>
+        <v>11.81212132863285</v>
       </c>
       <c r="E15">
-        <v>-6.824800000000001</v>
+        <v>-6.724400000000001</v>
       </c>
       <c r="F15">
-        <v>1.3052</v>
+        <v>1.4056</v>
       </c>
       <c r="G15">
         <v>0.157</v>
@@ -2502,28 +2502,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M15">
-        <v>0.06565156</v>
+        <v>0.07070168</v>
       </c>
       <c r="N15">
-        <v>1.134681773333333</v>
+        <v>1.129631653333333</v>
       </c>
       <c r="O15">
-        <v>0.3404045319999999</v>
+        <v>0.338889496</v>
       </c>
       <c r="P15">
-        <v>0.7942772413333332</v>
+        <v>0.7907421573333333</v>
       </c>
       <c r="Q15">
-        <v>0.8422772413333333</v>
+        <v>0.8387421573333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1583999660234873</v>
+        <v>0.1593536719041886</v>
       </c>
       <c r="T15">
-        <v>0.785096794776392</v>
+        <v>0.7917464542438009</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.28339392595291</v>
+        <v>16.97743721695628</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2548,22 +2548,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1419735578376022</v>
+        <v>0.1415618452347705</v>
       </c>
       <c r="C16">
-        <v>10.56352132863285</v>
+        <v>10.51390563845117</v>
       </c>
       <c r="D16">
-        <v>11.81212132863285</v>
+        <v>11.86290563845117</v>
       </c>
       <c r="E16">
-        <v>-6.724400000000001</v>
+        <v>-6.624000000000001</v>
       </c>
       <c r="F16">
-        <v>1.4056</v>
+        <v>1.506</v>
       </c>
       <c r="G16">
         <v>0.157</v>
@@ -2584,28 +2584,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M16">
-        <v>0.07070168</v>
+        <v>0.07575180000000002</v>
       </c>
       <c r="N16">
-        <v>1.129631653333333</v>
+        <v>1.124581533333333</v>
       </c>
       <c r="O16">
-        <v>0.338889496</v>
+        <v>0.33737446</v>
       </c>
       <c r="P16">
-        <v>0.7907421573333333</v>
+        <v>0.7872070733333334</v>
       </c>
       <c r="Q16">
-        <v>0.8387421573333333</v>
+        <v>0.8352070733333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1593536719041886</v>
+        <v>0.1603298179232594</v>
       </c>
       <c r="T16">
-        <v>0.7917464542438009</v>
+        <v>0.7985525762869136</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.97743721695628</v>
+        <v>15.84560806915919</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2630,22 +2630,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1415618452347705</v>
+        <v>0.1411501326319387</v>
       </c>
       <c r="C17">
-        <v>10.51390563845117</v>
+        <v>10.46472851169464</v>
       </c>
       <c r="D17">
-        <v>11.86290563845117</v>
+        <v>11.91412851169464</v>
       </c>
       <c r="E17">
-        <v>-6.624000000000001</v>
+        <v>-6.5236</v>
       </c>
       <c r="F17">
-        <v>1.506</v>
+        <v>1.6064</v>
       </c>
       <c r="G17">
         <v>0.157</v>
@@ -2666,28 +2666,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M17">
-        <v>0.07575179999999999</v>
+        <v>0.08080192000000001</v>
       </c>
       <c r="N17">
-        <v>1.124581533333333</v>
+        <v>1.119531413333333</v>
       </c>
       <c r="O17">
-        <v>0.33737446</v>
+        <v>0.335859424</v>
       </c>
       <c r="P17">
-        <v>0.7872070733333334</v>
+        <v>0.7836719893333333</v>
       </c>
       <c r="Q17">
-        <v>0.8352070733333334</v>
+        <v>0.8316719893333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1603298179232594</v>
+        <v>0.1613292055142128</v>
       </c>
       <c r="T17">
-        <v>0.7985525762869136</v>
+        <v>0.8055207488548621</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.84560806915919</v>
+        <v>14.85525756483674</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2712,22 +2712,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1411501326319387</v>
+        <v>0.140738420029107</v>
       </c>
       <c r="C18">
-        <v>10.46472851169464</v>
+        <v>10.41599565402245</v>
       </c>
       <c r="D18">
-        <v>11.91412851169464</v>
+        <v>11.96579565402245</v>
       </c>
       <c r="E18">
-        <v>-6.5236</v>
+        <v>-6.4232</v>
       </c>
       <c r="F18">
-        <v>1.6064</v>
+        <v>1.7068</v>
       </c>
       <c r="G18">
         <v>0.157</v>
@@ -2748,28 +2748,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M18">
-        <v>0.08080192000000001</v>
+        <v>0.08585204000000002</v>
       </c>
       <c r="N18">
-        <v>1.119531413333333</v>
+        <v>1.114481293333333</v>
       </c>
       <c r="O18">
-        <v>0.335859424</v>
+        <v>0.3343443879999999</v>
       </c>
       <c r="P18">
-        <v>0.7836719893333333</v>
+        <v>0.7801369053333334</v>
       </c>
       <c r="Q18">
-        <v>0.8316719893333333</v>
+        <v>0.8281369053333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1613292055142128</v>
+        <v>0.1623526747338639</v>
       </c>
       <c r="T18">
-        <v>0.8055207488548621</v>
+        <v>0.8126568291955325</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.85525756483674</v>
+        <v>13.98141888455222</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2794,22 +2794,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.140738420029107</v>
+        <v>0.1403267074262753</v>
       </c>
       <c r="C19">
-        <v>10.41599565402245</v>
+        <v>10.36771287049815</v>
       </c>
       <c r="D19">
-        <v>11.96579565402245</v>
+        <v>12.01791287049815</v>
       </c>
       <c r="E19">
-        <v>-6.4232</v>
+        <v>-6.322800000000001</v>
       </c>
       <c r="F19">
-        <v>1.7068</v>
+        <v>1.8072</v>
       </c>
       <c r="G19">
         <v>0.157</v>
@@ -2830,28 +2830,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M19">
-        <v>0.08585204000000002</v>
+        <v>0.09090216000000001</v>
       </c>
       <c r="N19">
-        <v>1.114481293333333</v>
+        <v>1.109431173333333</v>
       </c>
       <c r="O19">
-        <v>0.3343443879999999</v>
+        <v>0.332829352</v>
       </c>
       <c r="P19">
-        <v>0.7801369053333334</v>
+        <v>0.7766018213333333</v>
       </c>
       <c r="Q19">
-        <v>0.8281369053333334</v>
+        <v>0.8246018213333334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1623526747338639</v>
+        <v>0.1634011066174089</v>
       </c>
       <c r="T19">
-        <v>0.8126568291955325</v>
+        <v>0.8199669602762191</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.98141888455222</v>
+        <v>13.20467339096599</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2876,22 +2876,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1403267074262753</v>
+        <v>0.1401144948234435</v>
       </c>
       <c r="C20">
-        <v>10.36771287049815</v>
+        <v>10.29435381023523</v>
       </c>
       <c r="D20">
-        <v>12.01791287049815</v>
+        <v>12.04495381023523</v>
       </c>
       <c r="E20">
-        <v>-6.322800000000001</v>
+        <v>-6.2224</v>
       </c>
       <c r="F20">
-        <v>1.8072</v>
+        <v>1.9076</v>
       </c>
       <c r="G20">
         <v>0.157</v>
@@ -2912,45 +2912,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M20">
-        <v>0.09090216</v>
+        <v>0.09881368</v>
       </c>
       <c r="N20">
-        <v>1.109431173333333</v>
+        <v>1.101519653333333</v>
       </c>
       <c r="O20">
-        <v>0.332829352</v>
+        <v>0.330455896</v>
       </c>
       <c r="P20">
-        <v>0.7766018213333333</v>
+        <v>0.7710637573333334</v>
       </c>
       <c r="Q20">
-        <v>0.8246018213333334</v>
+        <v>0.8190637573333335</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1634011066174089</v>
+        <v>0.164475425707955</v>
       </c>
       <c r="T20">
-        <v>0.8199669602762191</v>
+        <v>0.8274575884206263</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.20467339096599</v>
+        <v>12.14744085366857</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2958,22 +2958,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1401144948234435</v>
+        <v>0.1397132822206118</v>
       </c>
       <c r="C21">
-        <v>10.29435381023523</v>
+        <v>10.24541178460183</v>
       </c>
       <c r="D21">
-        <v>12.04495381023523</v>
+        <v>12.09641178460184</v>
       </c>
       <c r="E21">
-        <v>-6.2224</v>
+        <v>-6.122</v>
       </c>
       <c r="F21">
-        <v>1.9076</v>
+        <v>2.008</v>
       </c>
       <c r="G21">
         <v>0.157</v>
@@ -2994,28 +2994,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M21">
-        <v>0.09881368</v>
+        <v>0.1040144</v>
       </c>
       <c r="N21">
-        <v>1.101519653333333</v>
+        <v>1.096318933333333</v>
       </c>
       <c r="O21">
-        <v>0.330455896</v>
+        <v>0.32889568</v>
       </c>
       <c r="P21">
-        <v>0.7710637573333334</v>
+        <v>0.7674232533333332</v>
       </c>
       <c r="Q21">
-        <v>0.8190637573333335</v>
+        <v>0.8154232533333332</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.164475425707955</v>
+        <v>0.1655766027757647</v>
       </c>
       <c r="T21">
-        <v>0.8274575884206263</v>
+        <v>0.8351354822686439</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.14744085366857</v>
+        <v>11.54006881098514</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3040,22 +3040,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1397132822206118</v>
+        <v>0.1393120696177801</v>
       </c>
       <c r="C22">
-        <v>10.24541178460183</v>
+        <v>10.19691131882091</v>
       </c>
       <c r="D22">
-        <v>12.09641178460184</v>
+        <v>12.14831131882091</v>
       </c>
       <c r="E22">
-        <v>-6.122</v>
+        <v>-6.0216</v>
       </c>
       <c r="F22">
-        <v>2.008</v>
+        <v>2.1084</v>
       </c>
       <c r="G22">
         <v>0.157</v>
@@ -3076,28 +3076,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M22">
-        <v>0.1040144</v>
+        <v>0.10921512</v>
       </c>
       <c r="N22">
-        <v>1.096318933333333</v>
+        <v>1.091118213333333</v>
       </c>
       <c r="O22">
-        <v>0.32889568</v>
+        <v>0.327335464</v>
       </c>
       <c r="P22">
-        <v>0.7674232533333332</v>
+        <v>0.7637827493333333</v>
       </c>
       <c r="Q22">
-        <v>0.8154232533333332</v>
+        <v>0.8117827493333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1655766027757647</v>
+        <v>0.1667056577440254</v>
       </c>
       <c r="T22">
-        <v>0.8351354822686439</v>
+        <v>0.8430077531761049</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.54006881098514</v>
+        <v>10.99054172474775</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3122,22 +3122,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1393120696177801</v>
+        <v>0.1389108570149483</v>
       </c>
       <c r="C23">
-        <v>10.19691131882091</v>
+        <v>10.14885812090708</v>
       </c>
       <c r="D23">
-        <v>12.14831131882091</v>
+        <v>12.20065812090708</v>
       </c>
       <c r="E23">
-        <v>-6.021600000000001</v>
+        <v>-5.921200000000001</v>
       </c>
       <c r="F23">
-        <v>2.1084</v>
+        <v>2.2088</v>
       </c>
       <c r="G23">
         <v>0.157</v>
@@ -3158,28 +3158,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M23">
-        <v>0.10921512</v>
+        <v>0.11441584</v>
       </c>
       <c r="N23">
-        <v>1.091118213333333</v>
+        <v>1.085917493333333</v>
       </c>
       <c r="O23">
-        <v>0.327335464</v>
+        <v>0.325775248</v>
       </c>
       <c r="P23">
-        <v>0.7637827493333333</v>
+        <v>0.7601422453333333</v>
       </c>
       <c r="Q23">
-        <v>0.8117827493333334</v>
+        <v>0.8081422453333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1667056577440254</v>
+        <v>0.1678636628396773</v>
       </c>
       <c r="T23">
-        <v>0.8430077531761048</v>
+        <v>0.8510818771837571</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.99054172474776</v>
+        <v>10.49097164635013</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3204,22 +3204,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1389108570149483</v>
+        <v>0.1385096444121166</v>
       </c>
       <c r="C24">
-        <v>10.14885812090708</v>
+        <v>10.10125799768354</v>
       </c>
       <c r="D24">
-        <v>12.20065812090708</v>
+        <v>12.25345799768354</v>
       </c>
       <c r="E24">
-        <v>-5.921200000000001</v>
+        <v>-5.8208</v>
       </c>
       <c r="F24">
-        <v>2.2088</v>
+        <v>2.3092</v>
       </c>
       <c r="G24">
         <v>0.157</v>
@@ -3240,28 +3240,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M24">
-        <v>0.11441584</v>
+        <v>0.11961656</v>
       </c>
       <c r="N24">
-        <v>1.085917493333333</v>
+        <v>1.080716773333333</v>
       </c>
       <c r="O24">
-        <v>0.325775248</v>
+        <v>0.324215032</v>
       </c>
       <c r="P24">
-        <v>0.7601422453333333</v>
+        <v>0.7565017413333333</v>
       </c>
       <c r="Q24">
-        <v>0.8081422453333333</v>
+        <v>0.8045017413333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1678636628396773</v>
+        <v>0.1690517459897618</v>
       </c>
       <c r="T24">
-        <v>0.8510818771837571</v>
+        <v>0.8593657186981015</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.49097164635013</v>
+        <v>10.03484244433491</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3286,22 +3286,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1385096444121166</v>
+        <v>0.1383940318092848</v>
       </c>
       <c r="C25">
-        <v>10.10125799768354</v>
+        <v>10.01615762493942</v>
       </c>
       <c r="D25">
-        <v>12.25345799768354</v>
+        <v>12.26875762493942</v>
       </c>
       <c r="E25">
-        <v>-5.8208</v>
+        <v>-5.7204</v>
       </c>
       <c r="F25">
-        <v>2.3092</v>
+        <v>2.409600000000001</v>
       </c>
       <c r="G25">
         <v>0.157</v>
@@ -3322,45 +3322,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M25">
-        <v>0.11961656</v>
+        <v>0.1289136</v>
       </c>
       <c r="N25">
-        <v>1.080716773333333</v>
+        <v>1.071419733333333</v>
       </c>
       <c r="O25">
-        <v>0.324215032</v>
+        <v>0.32142592</v>
       </c>
       <c r="P25">
-        <v>0.7565017413333333</v>
+        <v>0.7499938133333333</v>
       </c>
       <c r="Q25">
-        <v>0.8045017413333333</v>
+        <v>0.7979938133333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1690517459897618</v>
+        <v>0.1702710944859011</v>
       </c>
       <c r="T25">
-        <v>0.8593657186981015</v>
+        <v>0.867867556041771</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.03484244433491</v>
+        <v>9.311145863069008</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3368,22 +3368,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1383940318092848</v>
+        <v>0.1380047192064531</v>
       </c>
       <c r="C26">
-        <v>10.01615762493942</v>
+        <v>9.967559550107506</v>
       </c>
       <c r="D26">
-        <v>12.26875762493942</v>
+        <v>12.32055955010751</v>
       </c>
       <c r="E26">
-        <v>-5.720400000000001</v>
+        <v>-5.620000000000001</v>
       </c>
       <c r="F26">
-        <v>2.4096</v>
+        <v>2.51</v>
       </c>
       <c r="G26">
         <v>0.157</v>
@@ -3404,28 +3404,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M26">
-        <v>0.1289136</v>
+        <v>0.134285</v>
       </c>
       <c r="N26">
-        <v>1.071419733333333</v>
+        <v>1.066048333333333</v>
       </c>
       <c r="O26">
-        <v>0.32142592</v>
+        <v>0.3198144999999999</v>
       </c>
       <c r="P26">
-        <v>0.7499938133333333</v>
+        <v>0.7462338333333334</v>
       </c>
       <c r="Q26">
-        <v>0.7979938133333333</v>
+        <v>0.7942338333333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1702710944859011</v>
+        <v>0.1715229589419375</v>
       </c>
       <c r="T26">
-        <v>0.867867556041771</v>
+        <v>0.8765961090479383</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.31114586306901</v>
+        <v>8.938700028546251</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3450,22 +3450,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1380047192064531</v>
+        <v>0.1376154066036214</v>
       </c>
       <c r="C27">
-        <v>9.967559550107506</v>
+        <v>9.919400772841541</v>
       </c>
       <c r="D27">
-        <v>12.32055955010751</v>
+        <v>12.37280077284154</v>
       </c>
       <c r="E27">
-        <v>-5.620000000000001</v>
+        <v>-5.519600000000001</v>
       </c>
       <c r="F27">
-        <v>2.51</v>
+        <v>2.6104</v>
       </c>
       <c r="G27">
         <v>0.157</v>
@@ -3486,28 +3486,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M27">
-        <v>0.134285</v>
+        <v>0.1396564</v>
       </c>
       <c r="N27">
-        <v>1.066048333333333</v>
+        <v>1.060676933333333</v>
       </c>
       <c r="O27">
-        <v>0.3198144999999999</v>
+        <v>0.31820308</v>
       </c>
       <c r="P27">
-        <v>0.7462338333333334</v>
+        <v>0.7424738533333333</v>
       </c>
       <c r="Q27">
-        <v>0.7942338333333334</v>
+        <v>0.7904738533333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1715229589419375</v>
+        <v>0.1728086575724613</v>
       </c>
       <c r="T27">
-        <v>0.8765961090479383</v>
+        <v>0.88556056889211</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.938700028546251</v>
+        <v>8.594903873602163</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3532,22 +3532,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1376154066036214</v>
+        <v>0.1372260940007896</v>
       </c>
       <c r="C28">
-        <v>9.919400772841541</v>
+        <v>9.871686905021175</v>
       </c>
       <c r="D28">
-        <v>12.37280077284154</v>
+        <v>12.42548690502118</v>
       </c>
       <c r="E28">
-        <v>-5.519600000000001</v>
+        <v>-5.4192</v>
       </c>
       <c r="F28">
-        <v>2.6104</v>
+        <v>2.7108</v>
       </c>
       <c r="G28">
         <v>0.157</v>
@@ -3568,28 +3568,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M28">
-        <v>0.1396564</v>
+        <v>0.1450278</v>
       </c>
       <c r="N28">
-        <v>1.060676933333333</v>
+        <v>1.055305533333333</v>
       </c>
       <c r="O28">
-        <v>0.31820308</v>
+        <v>0.3165916599999999</v>
       </c>
       <c r="P28">
-        <v>0.7424738533333333</v>
+        <v>0.7387138733333333</v>
       </c>
       <c r="Q28">
-        <v>0.7904738533333333</v>
+        <v>0.7867138733333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1728086575724613</v>
+        <v>0.1741295808229995</v>
       </c>
       <c r="T28">
-        <v>0.88556056889211</v>
+        <v>0.8947706303758483</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.594903873602163</v>
+        <v>8.276574100505787</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3614,22 +3614,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1372260940007896</v>
+        <v>0.1368367813979579</v>
       </c>
       <c r="C29">
-        <v>9.871686905021175</v>
+        <v>9.824423654521354</v>
       </c>
       <c r="D29">
-        <v>12.42548690502118</v>
+        <v>12.47862365452135</v>
       </c>
       <c r="E29">
-        <v>-5.4192</v>
+        <v>-5.3188</v>
       </c>
       <c r="F29">
-        <v>2.7108</v>
+        <v>2.8112</v>
       </c>
       <c r="G29">
         <v>0.157</v>
@@ -3650,28 +3650,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M29">
-        <v>0.1450278</v>
+        <v>0.1503992</v>
       </c>
       <c r="N29">
-        <v>1.055305533333333</v>
+        <v>1.049934133333333</v>
       </c>
       <c r="O29">
-        <v>0.3165916599999999</v>
+        <v>0.31498024</v>
       </c>
       <c r="P29">
-        <v>0.7387138733333333</v>
+        <v>0.7349538933333333</v>
       </c>
       <c r="Q29">
-        <v>0.7867138733333333</v>
+        <v>0.7829538933333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1741295808229995</v>
+        <v>0.1754871963860526</v>
       </c>
       <c r="T29">
-        <v>0.8947706303758483</v>
+        <v>0.9042365269008011</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.276574100505787</v>
+        <v>7.980982168344865</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3696,22 +3696,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1368367813979579</v>
+        <v>0.1364474687951261</v>
       </c>
       <c r="C30">
-        <v>9.824423654521354</v>
+        <v>9.777616827273691</v>
       </c>
       <c r="D30">
-        <v>12.47862365452135</v>
+        <v>12.53221682727369</v>
       </c>
       <c r="E30">
-        <v>-5.3188</v>
+        <v>-5.218400000000001</v>
       </c>
       <c r="F30">
-        <v>2.8112</v>
+        <v>2.9116</v>
       </c>
       <c r="G30">
         <v>0.157</v>
@@ -3732,28 +3732,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M30">
-        <v>0.1503992</v>
+        <v>0.1557706</v>
       </c>
       <c r="N30">
-        <v>1.049934133333333</v>
+        <v>1.044562733333333</v>
       </c>
       <c r="O30">
-        <v>0.31498024</v>
+        <v>0.3133688199999999</v>
       </c>
       <c r="P30">
-        <v>0.7349538933333333</v>
+        <v>0.7311939133333332</v>
       </c>
       <c r="Q30">
-        <v>0.7829538933333333</v>
+        <v>0.7791939133333332</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1754871963860526</v>
+        <v>0.1768830546410227</v>
       </c>
       <c r="T30">
-        <v>0.9042365269008011</v>
+        <v>0.9139690683982882</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.980982168344865</v>
+        <v>7.705775886677801</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3778,22 +3778,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1364474687951261</v>
+        <v>0.1362261561922944</v>
       </c>
       <c r="C31">
-        <v>9.777616827273691</v>
+        <v>9.707888677566629</v>
       </c>
       <c r="D31">
-        <v>12.53221682727369</v>
+        <v>12.56288867756663</v>
       </c>
       <c r="E31">
-        <v>-5.218400000000001</v>
+        <v>-5.118</v>
       </c>
       <c r="F31">
-        <v>2.9116</v>
+        <v>3.012</v>
       </c>
       <c r="G31">
         <v>0.157</v>
@@ -3814,45 +3814,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M31">
-        <v>0.1557706</v>
+        <v>0.1635516</v>
       </c>
       <c r="N31">
-        <v>1.044562733333333</v>
+        <v>1.036781733333333</v>
       </c>
       <c r="O31">
-        <v>0.3133688199999999</v>
+        <v>0.31103452</v>
       </c>
       <c r="P31">
-        <v>0.7311939133333332</v>
+        <v>0.7257472133333334</v>
       </c>
       <c r="Q31">
-        <v>0.7791939133333332</v>
+        <v>0.7737472133333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1768830546410227</v>
+        <v>0.1783187945604206</v>
       </c>
       <c r="T31">
-        <v>0.9139690683982882</v>
+        <v>0.923979682509989</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.705775886677802</v>
+        <v>7.339172061498227</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3860,22 +3860,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1362261561922944</v>
+        <v>0.1358424435894627</v>
       </c>
       <c r="C32">
-        <v>9.707888677566629</v>
+        <v>9.661024971356401</v>
       </c>
       <c r="D32">
-        <v>12.56288867756663</v>
+        <v>12.6164249713564</v>
       </c>
       <c r="E32">
-        <v>-5.118</v>
+        <v>-5.017600000000001</v>
       </c>
       <c r="F32">
-        <v>3.012</v>
+        <v>3.1124</v>
       </c>
       <c r="G32">
         <v>0.157</v>
@@ -3896,28 +3896,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M32">
-        <v>0.1635516</v>
+        <v>0.16900332</v>
       </c>
       <c r="N32">
-        <v>1.036781733333333</v>
+        <v>1.031330013333333</v>
       </c>
       <c r="O32">
-        <v>0.31103452</v>
+        <v>0.3093990039999999</v>
       </c>
       <c r="P32">
-        <v>0.7257472133333334</v>
+        <v>0.7219310093333333</v>
       </c>
       <c r="Q32">
-        <v>0.7737472133333334</v>
+        <v>0.7699310093333334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1783187945604206</v>
+        <v>0.179796150129656</v>
       </c>
       <c r="T32">
-        <v>0.923979682509989</v>
+        <v>0.9342804593495652</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.339172061498227</v>
+        <v>7.102424575643443</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3942,22 +3942,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1358424435894627</v>
+        <v>0.1354587309866309</v>
       </c>
       <c r="C33">
-        <v>9.661024971356401</v>
+        <v>9.61461950385667</v>
       </c>
       <c r="D33">
-        <v>12.6164249713564</v>
+        <v>12.67041950385667</v>
       </c>
       <c r="E33">
-        <v>-5.017600000000001</v>
+        <v>-4.9172</v>
       </c>
       <c r="F33">
-        <v>3.1124</v>
+        <v>3.212800000000001</v>
       </c>
       <c r="G33">
         <v>0.157</v>
@@ -3978,28 +3978,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M33">
-        <v>0.16900332</v>
+        <v>0.17445504</v>
       </c>
       <c r="N33">
-        <v>1.031330013333333</v>
+        <v>1.025878293333333</v>
       </c>
       <c r="O33">
-        <v>0.3093990039999999</v>
+        <v>0.307763488</v>
       </c>
       <c r="P33">
-        <v>0.7219310093333333</v>
+        <v>0.7181148053333333</v>
       </c>
       <c r="Q33">
-        <v>0.7699310093333334</v>
+        <v>0.7661148053333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.179796150129656</v>
+        <v>0.1813169573332808</v>
       </c>
       <c r="T33">
-        <v>0.9342804593495652</v>
+        <v>0.9448842002138349</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.102424575643443</v>
+        <v>6.880473807654585</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4024,22 +4024,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1354587309866309</v>
+        <v>0.1350750183837992</v>
       </c>
       <c r="C34">
-        <v>9.61461950385667</v>
+        <v>9.568678183729395</v>
       </c>
       <c r="D34">
-        <v>12.67041950385667</v>
+        <v>12.72487818372939</v>
       </c>
       <c r="E34">
-        <v>-4.9172</v>
+        <v>-4.816800000000001</v>
       </c>
       <c r="F34">
-        <v>3.212800000000001</v>
+        <v>3.313200000000001</v>
       </c>
       <c r="G34">
         <v>0.157</v>
@@ -4060,28 +4060,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M34">
-        <v>0.17445504</v>
+        <v>0.17990676</v>
       </c>
       <c r="N34">
-        <v>1.025878293333333</v>
+        <v>1.020426573333333</v>
       </c>
       <c r="O34">
-        <v>0.307763488</v>
+        <v>0.306127972</v>
       </c>
       <c r="P34">
-        <v>0.7181148053333333</v>
+        <v>0.7142986013333333</v>
       </c>
       <c r="Q34">
-        <v>0.7661148053333333</v>
+        <v>0.7622986013333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1813169573332808</v>
+        <v>0.1828831617668645</v>
       </c>
       <c r="T34">
-        <v>0.9448842002138349</v>
+        <v>0.9558044706561426</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.880473807654585</v>
+        <v>6.671974601362023</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4106,22 +4106,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1350750183837992</v>
+        <v>0.1346913057809674</v>
       </c>
       <c r="C35">
-        <v>9.568678183729395</v>
+        <v>9.523207021659024</v>
       </c>
       <c r="D35">
-        <v>12.72487818372939</v>
+        <v>12.77980702165902</v>
       </c>
       <c r="E35">
-        <v>-4.816800000000001</v>
+        <v>-4.7164</v>
       </c>
       <c r="F35">
-        <v>3.313200000000001</v>
+        <v>3.413600000000001</v>
       </c>
       <c r="G35">
         <v>0.157</v>
@@ -4142,28 +4142,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M35">
-        <v>0.17990676</v>
+        <v>0.18535848</v>
       </c>
       <c r="N35">
-        <v>1.020426573333333</v>
+        <v>1.014974853333333</v>
       </c>
       <c r="O35">
-        <v>0.306127972</v>
+        <v>0.3044924559999999</v>
       </c>
       <c r="P35">
-        <v>0.7142986013333333</v>
+        <v>0.7104823973333332</v>
       </c>
       <c r="Q35">
-        <v>0.7622986013333334</v>
+        <v>0.7584823973333332</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1828831617668645</v>
+        <v>0.1844968269408598</v>
       </c>
       <c r="T35">
-        <v>0.9558044706561426</v>
+        <v>0.9670556583845805</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.671974601362023</v>
+        <v>6.475740054263139</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4188,22 +4188,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1346913057809674</v>
+        <v>0.1343075931781357</v>
       </c>
       <c r="C36">
-        <v>9.523207021659024</v>
+        <v>9.478212132564009</v>
       </c>
       <c r="D36">
-        <v>12.77980702165902</v>
+        <v>12.83521213256401</v>
       </c>
       <c r="E36">
-        <v>-4.7164</v>
+        <v>-4.616</v>
       </c>
       <c r="F36">
-        <v>3.413600000000001</v>
+        <v>3.514000000000001</v>
       </c>
       <c r="G36">
         <v>0.157</v>
@@ -4224,28 +4224,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M36">
-        <v>0.18535848</v>
+        <v>0.1908102</v>
       </c>
       <c r="N36">
-        <v>1.014974853333333</v>
+        <v>1.009523133333333</v>
       </c>
       <c r="O36">
-        <v>0.3044924559999999</v>
+        <v>0.30285694</v>
       </c>
       <c r="P36">
-        <v>0.7104823973333332</v>
+        <v>0.7066661933333332</v>
       </c>
       <c r="Q36">
-        <v>0.7584823973333332</v>
+        <v>0.7546661933333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1844968269408598</v>
+        <v>0.186160143350978</v>
       </c>
       <c r="T36">
-        <v>0.9670556583845805</v>
+        <v>0.9786530365046628</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.475740054263139</v>
+        <v>6.290718909855621</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4270,22 +4270,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1343075931781357</v>
+        <v>0.133923880575304</v>
       </c>
       <c r="C37">
-        <v>9.478212132564009</v>
+        <v>9.433699737866124</v>
       </c>
       <c r="D37">
-        <v>12.83521213256401</v>
+        <v>12.89109973786612</v>
       </c>
       <c r="E37">
-        <v>-4.616</v>
+        <v>-4.5156</v>
       </c>
       <c r="F37">
-        <v>3.514000000000001</v>
+        <v>3.614400000000001</v>
       </c>
       <c r="G37">
         <v>0.157</v>
@@ -4306,28 +4306,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M37">
-        <v>0.1908102</v>
+        <v>0.19626192</v>
       </c>
       <c r="N37">
-        <v>1.009523133333333</v>
+        <v>1.004071413333333</v>
       </c>
       <c r="O37">
-        <v>0.30285694</v>
+        <v>0.301221424</v>
       </c>
       <c r="P37">
-        <v>0.7066661933333332</v>
+        <v>0.7028499893333333</v>
       </c>
       <c r="Q37">
-        <v>0.7546661933333333</v>
+        <v>0.7508499893333334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.186160143350978</v>
+        <v>0.1878754383989125</v>
       </c>
       <c r="T37">
-        <v>0.9786530365046628</v>
+        <v>0.9906128326909979</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.290718909855621</v>
+        <v>6.115976717915188</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4352,22 +4352,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.133923880575304</v>
+        <v>0.1337991679724722</v>
       </c>
       <c r="C38">
-        <v>9.433699737866124</v>
+        <v>9.351569031073257</v>
       </c>
       <c r="D38">
-        <v>12.89109973786612</v>
+        <v>12.90936903107326</v>
       </c>
       <c r="E38">
-        <v>-4.515600000000001</v>
+        <v>-4.4152</v>
       </c>
       <c r="F38">
-        <v>3.6144</v>
+        <v>3.7148</v>
       </c>
       <c r="G38">
         <v>0.157</v>
@@ -4388,45 +4388,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M38">
-        <v>0.19626192</v>
+        <v>0.20542844</v>
       </c>
       <c r="N38">
-        <v>1.004071413333333</v>
+        <v>0.9949048933333332</v>
       </c>
       <c r="O38">
-        <v>0.301221424</v>
+        <v>0.298471468</v>
       </c>
       <c r="P38">
-        <v>0.7028499893333333</v>
+        <v>0.6964334253333333</v>
       </c>
       <c r="Q38">
-        <v>0.7508499893333334</v>
+        <v>0.7444334253333333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1878754383989125</v>
+        <v>0.1896451872578924</v>
       </c>
       <c r="T38">
-        <v>0.9906128326909979</v>
+        <v>1.00295230494674</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.115976717915188</v>
+        <v>5.84307281568868</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4434,22 +4434,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1337991679724722</v>
+        <v>0.1334224553696405</v>
       </c>
       <c r="C39">
-        <v>9.351569031073257</v>
+        <v>9.306669895413288</v>
       </c>
       <c r="D39">
-        <v>12.90936903107326</v>
+        <v>12.96486989541329</v>
       </c>
       <c r="E39">
-        <v>-4.4152</v>
+        <v>-4.3148</v>
       </c>
       <c r="F39">
-        <v>3.7148</v>
+        <v>3.8152</v>
       </c>
       <c r="G39">
         <v>0.157</v>
@@ -4470,28 +4470,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M39">
-        <v>0.20542844</v>
+        <v>0.21098056</v>
       </c>
       <c r="N39">
-        <v>0.9949048933333332</v>
+        <v>0.9893527733333332</v>
       </c>
       <c r="O39">
-        <v>0.298471468</v>
+        <v>0.2968058319999999</v>
       </c>
       <c r="P39">
-        <v>0.6964334253333333</v>
+        <v>0.6925469413333332</v>
       </c>
       <c r="Q39">
-        <v>0.7444334253333333</v>
+        <v>0.7405469413333332</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1896451872578924</v>
+        <v>0.1914720247897427</v>
       </c>
       <c r="T39">
-        <v>1.00295230494674</v>
+        <v>1.015689824694603</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.84307281568868</v>
+        <v>5.689307741591609</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4516,22 +4516,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1334224553696405</v>
+        <v>0.1330457427668088</v>
       </c>
       <c r="C40">
-        <v>9.306669895413288</v>
+        <v>9.26225004675122</v>
       </c>
       <c r="D40">
-        <v>12.96486989541329</v>
+        <v>13.02085004675122</v>
       </c>
       <c r="E40">
-        <v>-4.3148</v>
+        <v>-4.2144</v>
       </c>
       <c r="F40">
-        <v>3.8152</v>
+        <v>3.9156</v>
       </c>
       <c r="G40">
         <v>0.157</v>
@@ -4552,28 +4552,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M40">
-        <v>0.21098056</v>
+        <v>0.21653268</v>
       </c>
       <c r="N40">
-        <v>0.9893527733333332</v>
+        <v>0.9838006533333332</v>
       </c>
       <c r="O40">
-        <v>0.2968058319999999</v>
+        <v>0.295140196</v>
       </c>
       <c r="P40">
-        <v>0.6925469413333332</v>
+        <v>0.6886604573333333</v>
       </c>
       <c r="Q40">
-        <v>0.7405469413333332</v>
+        <v>0.7366604573333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1914720247897427</v>
+        <v>0.1933587586341127</v>
       </c>
       <c r="T40">
-        <v>1.015689824694603</v>
+        <v>1.028844968040757</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.689307741591609</v>
+        <v>5.543428055909773</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4598,22 +4598,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1330457427668088</v>
+        <v>0.132669030163977</v>
       </c>
       <c r="C41">
-        <v>9.26225004675122</v>
+        <v>9.218315720454893</v>
       </c>
       <c r="D41">
-        <v>13.02085004675122</v>
+        <v>13.07731572045489</v>
       </c>
       <c r="E41">
-        <v>-4.2144</v>
+        <v>-4.114</v>
       </c>
       <c r="F41">
-        <v>3.9156</v>
+        <v>4.016000000000001</v>
       </c>
       <c r="G41">
         <v>0.157</v>
@@ -4634,28 +4634,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M41">
-        <v>0.21653268</v>
+        <v>0.2220848000000001</v>
       </c>
       <c r="N41">
-        <v>0.9838006533333332</v>
+        <v>0.9782485333333332</v>
       </c>
       <c r="O41">
-        <v>0.295140196</v>
+        <v>0.2934745599999999</v>
       </c>
       <c r="P41">
-        <v>0.6886604573333333</v>
+        <v>0.6847739733333332</v>
       </c>
       <c r="Q41">
-        <v>0.7366604573333333</v>
+        <v>0.7327739733333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1933587586341127</v>
+        <v>0.1953083836066283</v>
       </c>
       <c r="T41">
-        <v>1.028844968040757</v>
+        <v>1.042438616165116</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.543428055909773</v>
+        <v>5.404842354512028</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4680,22 +4680,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.132669030163977</v>
+        <v>0.1322923175611453</v>
       </c>
       <c r="C42">
-        <v>9.218315720454893</v>
+        <v>9.174873260523375</v>
       </c>
       <c r="D42">
-        <v>13.07731572045489</v>
+        <v>13.13427326052338</v>
       </c>
       <c r="E42">
-        <v>-4.114</v>
+        <v>-4.0136</v>
       </c>
       <c r="F42">
-        <v>4.016000000000001</v>
+        <v>4.116400000000001</v>
       </c>
       <c r="G42">
         <v>0.157</v>
@@ -4716,28 +4716,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M42">
-        <v>0.2220848000000001</v>
+        <v>0.22763692</v>
       </c>
       <c r="N42">
-        <v>0.9782485333333332</v>
+        <v>0.9726964133333332</v>
       </c>
       <c r="O42">
-        <v>0.2934745599999999</v>
+        <v>0.291808924</v>
       </c>
       <c r="P42">
-        <v>0.6847739733333332</v>
+        <v>0.6808874893333332</v>
       </c>
       <c r="Q42">
-        <v>0.7327739733333333</v>
+        <v>0.7288874893333332</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1953083836066283</v>
+        <v>0.1973240975612632</v>
       </c>
       <c r="T42">
-        <v>1.042438616165116</v>
+        <v>1.056493065920809</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.404842354512028</v>
+        <v>5.273016931231248</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4762,22 +4762,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1322923175611453</v>
+        <v>0.1319156049583135</v>
       </c>
       <c r="C43">
-        <v>9.174873260523375</v>
+        <v>9.131929121963012</v>
       </c>
       <c r="D43">
-        <v>13.13427326052338</v>
+        <v>13.19172912196301</v>
       </c>
       <c r="E43">
-        <v>-4.0136</v>
+        <v>-3.9132</v>
       </c>
       <c r="F43">
-        <v>4.116400000000001</v>
+        <v>4.216800000000001</v>
       </c>
       <c r="G43">
         <v>0.157</v>
@@ -4798,28 +4798,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M43">
-        <v>0.22763692</v>
+        <v>0.2331890400000001</v>
       </c>
       <c r="N43">
-        <v>0.9726964133333332</v>
+        <v>0.9671442933333332</v>
       </c>
       <c r="O43">
-        <v>0.291808924</v>
+        <v>0.2901432879999999</v>
       </c>
       <c r="P43">
-        <v>0.6808874893333332</v>
+        <v>0.6770010053333333</v>
       </c>
       <c r="Q43">
-        <v>0.7288874893333332</v>
+        <v>0.7250010053333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1973240975612632</v>
+        <v>0.199409318893644</v>
       </c>
       <c r="T43">
-        <v>1.056493065920809</v>
+        <v>1.071032151874974</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.273016931231248</v>
+        <v>5.147468909059074</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4844,22 +4844,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1319156049583135</v>
+        <v>0.1315388923554818</v>
       </c>
       <c r="C44">
-        <v>9.131929121963008</v>
+        <v>9.089489873226064</v>
       </c>
       <c r="D44">
-        <v>13.19172912196301</v>
+        <v>13.24968987322607</v>
       </c>
       <c r="E44">
-        <v>-3.913200000000001</v>
+        <v>-3.8128</v>
       </c>
       <c r="F44">
-        <v>4.2168</v>
+        <v>4.317200000000001</v>
       </c>
       <c r="G44">
         <v>0.157</v>
@@ -4880,28 +4880,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M44">
-        <v>0.23318904</v>
+        <v>0.23874116</v>
       </c>
       <c r="N44">
-        <v>0.9671442933333332</v>
+        <v>0.9615921733333332</v>
       </c>
       <c r="O44">
-        <v>0.2901432879999999</v>
+        <v>0.288477652</v>
       </c>
       <c r="P44">
-        <v>0.6770010053333333</v>
+        <v>0.6731145213333333</v>
       </c>
       <c r="Q44">
-        <v>0.7250010053333333</v>
+        <v>0.7211145213333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.199409318893644</v>
+        <v>0.2015677058868101</v>
       </c>
       <c r="T44">
-        <v>1.071032151874974</v>
+        <v>1.086081381195952</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.147468909059076</v>
+        <v>5.027760329778632</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4926,22 +4926,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1315388923554818</v>
+        <v>0.13116217975265</v>
       </c>
       <c r="C45">
-        <v>9.089489873226064</v>
+        <v>9.047562198713997</v>
       </c>
       <c r="D45">
-        <v>13.24968987322607</v>
+        <v>13.308162198714</v>
       </c>
       <c r="E45">
-        <v>-3.8128</v>
+        <v>-3.712400000000001</v>
       </c>
       <c r="F45">
-        <v>4.317200000000001</v>
+        <v>4.4176</v>
       </c>
       <c r="G45">
         <v>0.157</v>
@@ -4962,28 +4962,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M45">
-        <v>0.23874116</v>
+        <v>0.24429328</v>
       </c>
       <c r="N45">
-        <v>0.9615921733333332</v>
+        <v>0.9560400533333332</v>
       </c>
       <c r="O45">
-        <v>0.288477652</v>
+        <v>0.2868120159999999</v>
       </c>
       <c r="P45">
-        <v>0.6731145213333333</v>
+        <v>0.6692280373333332</v>
       </c>
       <c r="Q45">
-        <v>0.7211145213333333</v>
+        <v>0.7172280373333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2015677058868101</v>
+        <v>0.2038031781297322</v>
       </c>
       <c r="T45">
-        <v>1.086081381195952</v>
+        <v>1.101668082992679</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.027760329778632</v>
+        <v>4.91349304955639</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5008,22 +5008,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.13116217975265</v>
+        <v>0.1307854671498183</v>
       </c>
       <c r="C46">
-        <v>9.047562198713997</v>
+        <v>9.006152901347267</v>
       </c>
       <c r="D46">
-        <v>13.308162198714</v>
+        <v>13.36715290134727</v>
       </c>
       <c r="E46">
-        <v>-3.712400000000001</v>
+        <v>-3.612</v>
       </c>
       <c r="F46">
-        <v>4.4176</v>
+        <v>4.518000000000001</v>
       </c>
       <c r="G46">
         <v>0.157</v>
@@ -5044,28 +5044,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M46">
-        <v>0.24429328</v>
+        <v>0.2498454000000001</v>
       </c>
       <c r="N46">
-        <v>0.9560400533333332</v>
+        <v>0.9504879333333331</v>
       </c>
       <c r="O46">
-        <v>0.2868120159999999</v>
+        <v>0.2851463799999999</v>
       </c>
       <c r="P46">
-        <v>0.6692280373333332</v>
+        <v>0.6653415533333332</v>
       </c>
       <c r="Q46">
-        <v>0.7172280373333333</v>
+        <v>0.7133415533333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2038031781297322</v>
+        <v>0.2061199402723969</v>
       </c>
       <c r="T46">
-        <v>1.101668082992679</v>
+        <v>1.117821573945651</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.91349304955639</v>
+        <v>4.804304315121803</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5090,22 +5090,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1307854671498183</v>
+        <v>0.1304087545469866</v>
       </c>
       <c r="C47">
-        <v>9.006152901347267</v>
+        <v>8.965268905203818</v>
       </c>
       <c r="D47">
-        <v>13.36715290134727</v>
+        <v>13.42666890520382</v>
       </c>
       <c r="E47">
-        <v>-3.612</v>
+        <v>-3.5116</v>
       </c>
       <c r="F47">
-        <v>4.518000000000001</v>
+        <v>4.6184</v>
       </c>
       <c r="G47">
         <v>0.157</v>
@@ -5126,28 +5126,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M47">
-        <v>0.2498454000000001</v>
+        <v>0.25539752</v>
       </c>
       <c r="N47">
-        <v>0.9504879333333331</v>
+        <v>0.9449358133333332</v>
       </c>
       <c r="O47">
-        <v>0.2851463799999999</v>
+        <v>0.283480744</v>
       </c>
       <c r="P47">
-        <v>0.6653415533333332</v>
+        <v>0.6614550693333332</v>
       </c>
       <c r="Q47">
-        <v>0.7133415533333333</v>
+        <v>0.7094550693333332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2061199402723969</v>
+        <v>0.2085225084203455</v>
       </c>
       <c r="T47">
-        <v>1.117821573945651</v>
+        <v>1.134573342341325</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.804304315121803</v>
+        <v>4.699862916966982</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5172,22 +5172,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1304087545469866</v>
+        <v>0.1300320419441548</v>
       </c>
       <c r="C48">
-        <v>8.965268905203818</v>
+        <v>8.924917258228344</v>
       </c>
       <c r="D48">
-        <v>13.42666890520382</v>
+        <v>13.48671725822834</v>
       </c>
       <c r="E48">
-        <v>-3.5116</v>
+        <v>-3.4112</v>
       </c>
       <c r="F48">
-        <v>4.6184</v>
+        <v>4.718800000000001</v>
       </c>
       <c r="G48">
         <v>0.157</v>
@@ -5208,28 +5208,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M48">
-        <v>0.25539752</v>
+        <v>0.26094964</v>
       </c>
       <c r="N48">
-        <v>0.9449358133333332</v>
+        <v>0.9393836933333333</v>
       </c>
       <c r="O48">
-        <v>0.283480744</v>
+        <v>0.281815108</v>
       </c>
       <c r="P48">
-        <v>0.6614550693333332</v>
+        <v>0.6575685853333333</v>
       </c>
       <c r="Q48">
-        <v>0.7094550693333332</v>
+        <v>0.7055685853333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2085225084203455</v>
+        <v>0.2110157395172733</v>
       </c>
       <c r="T48">
-        <v>1.134573342341325</v>
+        <v>1.15195725294061</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.699862916966982</v>
+        <v>4.599865833627259</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5254,22 +5254,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1300320419441548</v>
+        <v>0.1296553293413231</v>
       </c>
       <c r="C49">
-        <v>8.924917258228344</v>
+        <v>8.885105135014598</v>
       </c>
       <c r="D49">
-        <v>13.48671725822834</v>
+        <v>13.5473051350146</v>
       </c>
       <c r="E49">
-        <v>-3.4112</v>
+        <v>-3.3108</v>
       </c>
       <c r="F49">
-        <v>4.718800000000001</v>
+        <v>4.819200000000001</v>
       </c>
       <c r="G49">
         <v>0.157</v>
@@ -5290,28 +5290,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M49">
-        <v>0.26094964</v>
+        <v>0.2665017600000001</v>
       </c>
       <c r="N49">
-        <v>0.9393836933333333</v>
+        <v>0.9338315733333331</v>
       </c>
       <c r="O49">
-        <v>0.281815108</v>
+        <v>0.2801494719999999</v>
       </c>
       <c r="P49">
-        <v>0.6575685853333333</v>
+        <v>0.6536821013333332</v>
       </c>
       <c r="Q49">
-        <v>0.7055685853333333</v>
+        <v>0.7016821013333332</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2110157395172733</v>
+        <v>0.213604864117929</v>
       </c>
       <c r="T49">
-        <v>1.15195725294061</v>
+        <v>1.170009775486021</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.599865833627259</v>
+        <v>4.504035295426689</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5336,22 +5336,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1296553293413231</v>
+        <v>0.1301361167384913</v>
       </c>
       <c r="C50">
-        <v>8.8851051350146</v>
+        <v>8.707474005263812</v>
       </c>
       <c r="D50">
-        <v>13.5473051350146</v>
+        <v>13.47007400526381</v>
       </c>
       <c r="E50">
-        <v>-3.3108</v>
+        <v>-3.210400000000001</v>
       </c>
       <c r="F50">
-        <v>4.8192</v>
+        <v>4.9196</v>
       </c>
       <c r="G50">
         <v>0.157</v>
@@ -5372,45 +5372,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M50">
-        <v>0.26650176</v>
+        <v>0.28435288</v>
       </c>
       <c r="N50">
-        <v>0.9338315733333332</v>
+        <v>0.9159804533333332</v>
       </c>
       <c r="O50">
-        <v>0.280149472</v>
+        <v>0.274794136</v>
       </c>
       <c r="P50">
-        <v>0.6536821013333333</v>
+        <v>0.6411863173333332</v>
       </c>
       <c r="Q50">
-        <v>0.7016821013333333</v>
+        <v>0.6891863173333332</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.213604864117929</v>
+        <v>0.2162955230166497</v>
       </c>
       <c r="T50">
-        <v>1.170009775486021</v>
+        <v>1.188770240092037</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.504035295426691</v>
+        <v>4.221280731650522</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5418,22 +5418,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1301361167384913</v>
+        <v>0.1297769041356596</v>
       </c>
       <c r="C51">
-        <v>8.707474005263812</v>
+        <v>8.66469247064509</v>
       </c>
       <c r="D51">
-        <v>13.47007400526381</v>
+        <v>13.52769247064509</v>
       </c>
       <c r="E51">
-        <v>-3.210400000000001</v>
+        <v>-3.11</v>
       </c>
       <c r="F51">
-        <v>4.9196</v>
+        <v>5.02</v>
       </c>
       <c r="G51">
         <v>0.157</v>
@@ -5454,28 +5454,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M51">
-        <v>0.28435288</v>
+        <v>0.290156</v>
       </c>
       <c r="N51">
-        <v>0.9159804533333332</v>
+        <v>0.9101773333333332</v>
       </c>
       <c r="O51">
-        <v>0.274794136</v>
+        <v>0.2730531999999999</v>
       </c>
       <c r="P51">
-        <v>0.6411863173333332</v>
+        <v>0.6371241333333333</v>
       </c>
       <c r="Q51">
-        <v>0.6891863173333332</v>
+        <v>0.6851241333333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2162955230166497</v>
+        <v>0.2190938082713192</v>
       </c>
       <c r="T51">
-        <v>1.188770240092037</v>
+        <v>1.208281123282293</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.221280731650522</v>
+        <v>4.136855117017511</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5500,22 +5500,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1297769041356596</v>
+        <v>0.1294176915328279</v>
       </c>
       <c r="C52">
-        <v>8.66469247064509</v>
+        <v>8.622405981477659</v>
       </c>
       <c r="D52">
-        <v>13.52769247064509</v>
+        <v>13.58580598147766</v>
       </c>
       <c r="E52">
-        <v>-3.11</v>
+        <v>-3.0096</v>
       </c>
       <c r="F52">
-        <v>5.02</v>
+        <v>5.120400000000001</v>
       </c>
       <c r="G52">
         <v>0.157</v>
@@ -5536,28 +5536,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M52">
-        <v>0.290156</v>
+        <v>0.2959591200000001</v>
       </c>
       <c r="N52">
-        <v>0.9101773333333332</v>
+        <v>0.9043742133333332</v>
       </c>
       <c r="O52">
-        <v>0.2730531999999999</v>
+        <v>0.271312264</v>
       </c>
       <c r="P52">
-        <v>0.6371241333333333</v>
+        <v>0.6330619493333333</v>
       </c>
       <c r="Q52">
-        <v>0.6851241333333333</v>
+        <v>0.6810619493333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2190938082713192</v>
+        <v>0.2220063092506691</v>
       </c>
       <c r="T52">
-        <v>1.208281123282293</v>
+        <v>1.228588369051744</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.136855117017511</v>
+        <v>4.055740310801482</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5582,22 +5582,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1294176915328279</v>
+        <v>0.1303324789299961</v>
       </c>
       <c r="C53">
-        <v>8.622405981477659</v>
+        <v>8.37498410007133</v>
       </c>
       <c r="D53">
-        <v>13.58580598147766</v>
+        <v>13.43878410007133</v>
       </c>
       <c r="E53">
-        <v>-3.0096</v>
+        <v>-2.9092</v>
       </c>
       <c r="F53">
-        <v>5.120400000000001</v>
+        <v>5.220800000000001</v>
       </c>
       <c r="G53">
         <v>0.157</v>
@@ -5618,45 +5618,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M53">
-        <v>0.2959591200000001</v>
+        <v>0.32003504</v>
       </c>
       <c r="N53">
-        <v>0.9043742133333332</v>
+        <v>0.8802982933333332</v>
       </c>
       <c r="O53">
-        <v>0.271312264</v>
+        <v>0.2640894879999999</v>
       </c>
       <c r="P53">
-        <v>0.6330619493333333</v>
+        <v>0.6162088053333332</v>
       </c>
       <c r="Q53">
-        <v>0.6810619493333333</v>
+        <v>0.6642088053333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2220063092506691</v>
+        <v>0.2250401644374919</v>
       </c>
       <c r="T53">
-        <v>1.228588369051744</v>
+        <v>1.249741750061588</v>
       </c>
       <c r="U53">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.055740310801482</v>
+        <v>3.750630972575169</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5664,22 +5664,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1303324789299961</v>
+        <v>0.1299977663271644</v>
       </c>
       <c r="C54">
-        <v>8.37498410007133</v>
+        <v>8.328007493603533</v>
       </c>
       <c r="D54">
-        <v>13.43878410007133</v>
+        <v>13.49220749360353</v>
       </c>
       <c r="E54">
-        <v>-2.9092</v>
+        <v>-2.8088</v>
       </c>
       <c r="F54">
-        <v>5.220800000000001</v>
+        <v>5.321200000000001</v>
       </c>
       <c r="G54">
         <v>0.157</v>
@@ -5700,28 +5700,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M54">
-        <v>0.32003504</v>
+        <v>0.32618956</v>
       </c>
       <c r="N54">
-        <v>0.8802982933333332</v>
+        <v>0.8741437733333333</v>
       </c>
       <c r="O54">
-        <v>0.2640894879999999</v>
+        <v>0.262243132</v>
       </c>
       <c r="P54">
-        <v>0.6162088053333332</v>
+        <v>0.6119006413333332</v>
       </c>
       <c r="Q54">
-        <v>0.6642088053333333</v>
+        <v>0.6599006413333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2250401644374919</v>
+        <v>0.2282031198450306</v>
       </c>
       <c r="T54">
-        <v>1.249741750061588</v>
+        <v>1.271795274944191</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.750630972575169</v>
+        <v>3.679864350451109</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5746,22 +5746,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1299977663271644</v>
+        <v>0.1296630537243326</v>
       </c>
       <c r="C55">
-        <v>8.328007493603533</v>
+        <v>8.281457331971865</v>
       </c>
       <c r="D55">
-        <v>13.49220749360353</v>
+        <v>13.54605733197187</v>
       </c>
       <c r="E55">
-        <v>-2.8088</v>
+        <v>-2.7084</v>
       </c>
       <c r="F55">
-        <v>5.321200000000001</v>
+        <v>5.421600000000001</v>
       </c>
       <c r="G55">
         <v>0.157</v>
@@ -5782,28 +5782,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M55">
-        <v>0.32618956</v>
+        <v>0.33234408</v>
       </c>
       <c r="N55">
-        <v>0.8741437733333333</v>
+        <v>0.8679892533333332</v>
       </c>
       <c r="O55">
-        <v>0.262243132</v>
+        <v>0.2603967759999999</v>
       </c>
       <c r="P55">
-        <v>0.6119006413333332</v>
+        <v>0.6075924773333332</v>
       </c>
       <c r="Q55">
-        <v>0.6599006413333333</v>
+        <v>0.6555924773333333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2282031198450306</v>
+        <v>0.2315035950528971</v>
       </c>
       <c r="T55">
-        <v>1.271795274944191</v>
+        <v>1.294807648734734</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.679864350451109</v>
+        <v>3.611718714331644</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5828,22 +5828,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1296630537243326</v>
+        <v>0.1293283411215009</v>
       </c>
       <c r="C56">
-        <v>8.281457331971865</v>
+        <v>8.235338741692392</v>
       </c>
       <c r="D56">
-        <v>13.54605733197187</v>
+        <v>13.60033874169239</v>
       </c>
       <c r="E56">
-        <v>-2.7084</v>
+        <v>-2.608</v>
       </c>
       <c r="F56">
-        <v>5.421600000000001</v>
+        <v>5.522000000000001</v>
       </c>
       <c r="G56">
         <v>0.157</v>
@@ -5864,28 +5864,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M56">
-        <v>0.33234408</v>
+        <v>0.3384986000000001</v>
       </c>
       <c r="N56">
-        <v>0.8679892533333332</v>
+        <v>0.8618347333333332</v>
       </c>
       <c r="O56">
-        <v>0.2603967759999999</v>
+        <v>0.2585504199999999</v>
       </c>
       <c r="P56">
-        <v>0.6075924773333332</v>
+        <v>0.6032843133333332</v>
       </c>
       <c r="Q56">
-        <v>0.6555924773333333</v>
+        <v>0.6512843133333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2315035950528971</v>
+        <v>0.2349507580477798</v>
       </c>
       <c r="T56">
-        <v>1.294807648734734</v>
+        <v>1.318842794693745</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.611718714331644</v>
+        <v>3.546051101343795</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5910,22 +5910,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1293283411215009</v>
+        <v>0.1300912285186692</v>
       </c>
       <c r="C57">
-        <v>8.235338741692392</v>
+        <v>8.011847321557754</v>
       </c>
       <c r="D57">
-        <v>13.60033874169239</v>
+        <v>13.47724732155775</v>
       </c>
       <c r="E57">
-        <v>-2.608</v>
+        <v>-2.5076</v>
       </c>
       <c r="F57">
-        <v>5.522000000000001</v>
+        <v>5.622400000000001</v>
       </c>
       <c r="G57">
         <v>0.157</v>
@@ -5946,45 +5946,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M57">
-        <v>0.3384986000000001</v>
+        <v>0.3603958400000001</v>
       </c>
       <c r="N57">
-        <v>0.8618347333333332</v>
+        <v>0.8399374933333332</v>
       </c>
       <c r="O57">
-        <v>0.2585504199999999</v>
+        <v>0.2519812479999999</v>
       </c>
       <c r="P57">
-        <v>0.6032843133333332</v>
+        <v>0.5879562453333333</v>
       </c>
       <c r="Q57">
-        <v>0.6512843133333333</v>
+        <v>0.6359562453333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2349507580477798</v>
+        <v>0.2385546102697027</v>
       </c>
       <c r="T57">
-        <v>1.318842794693745</v>
+        <v>1.343970447287257</v>
       </c>
       <c r="U57">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.546051101343795</v>
+        <v>3.330597082733622</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5992,22 +5992,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1300912285186692</v>
+        <v>0.1297761159158374</v>
       </c>
       <c r="C58">
-        <v>8.011847321557754</v>
+        <v>7.962019444788119</v>
       </c>
       <c r="D58">
-        <v>13.47724732155775</v>
+        <v>13.52781944478812</v>
       </c>
       <c r="E58">
-        <v>-2.5076</v>
+        <v>-2.4072</v>
       </c>
       <c r="F58">
-        <v>5.622400000000001</v>
+        <v>5.722800000000001</v>
       </c>
       <c r="G58">
         <v>0.157</v>
@@ -6028,28 +6028,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M58">
-        <v>0.3603958400000001</v>
+        <v>0.3668314800000001</v>
       </c>
       <c r="N58">
-        <v>0.8399374933333332</v>
+        <v>0.8335018533333332</v>
       </c>
       <c r="O58">
-        <v>0.2519812479999999</v>
+        <v>0.2500505559999999</v>
       </c>
       <c r="P58">
-        <v>0.5879562453333333</v>
+        <v>0.5834512973333332</v>
       </c>
       <c r="Q58">
-        <v>0.6359562453333334</v>
+        <v>0.6314512973333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2385546102697027</v>
+        <v>0.2423260835252033</v>
       </c>
       <c r="T58">
-        <v>1.343970447287257</v>
+        <v>1.370266827908374</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.330597082733622</v>
+        <v>3.272165554966365</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6074,22 +6074,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1297761159158374</v>
+        <v>0.1294610033130057</v>
       </c>
       <c r="C59">
-        <v>7.962019444788119</v>
+        <v>7.912572531974233</v>
       </c>
       <c r="D59">
-        <v>13.52781944478812</v>
+        <v>13.57877253197423</v>
       </c>
       <c r="E59">
-        <v>-2.4072</v>
+        <v>-2.3068</v>
       </c>
       <c r="F59">
-        <v>5.722800000000001</v>
+        <v>5.823200000000001</v>
       </c>
       <c r="G59">
         <v>0.157</v>
@@ -6110,28 +6110,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M59">
-        <v>0.3668314800000001</v>
+        <v>0.3732671200000001</v>
       </c>
       <c r="N59">
-        <v>0.8335018533333332</v>
+        <v>0.8270662133333332</v>
       </c>
       <c r="O59">
-        <v>0.2500505559999999</v>
+        <v>0.2481198639999999</v>
       </c>
       <c r="P59">
-        <v>0.5834512973333332</v>
+        <v>0.5789463493333332</v>
       </c>
       <c r="Q59">
-        <v>0.6314512973333333</v>
+        <v>0.6269463493333333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2423260835252033</v>
+        <v>0.2462771507452516</v>
       </c>
       <c r="T59">
-        <v>1.370266827908374</v>
+        <v>1.397815417130496</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.272165554966365</v>
+        <v>3.215748907466945</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6156,22 +6156,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1294610033130057</v>
+        <v>0.1291458907101739</v>
       </c>
       <c r="C60">
-        <v>7.912572531974231</v>
+        <v>7.863510904140536</v>
       </c>
       <c r="D60">
-        <v>13.57877253197423</v>
+        <v>13.63011090414054</v>
       </c>
       <c r="E60">
-        <v>-2.306800000000001</v>
+        <v>-2.2064</v>
       </c>
       <c r="F60">
-        <v>5.8232</v>
+        <v>5.9236</v>
       </c>
       <c r="G60">
         <v>0.157</v>
@@ -6192,28 +6192,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M60">
-        <v>0.37326712</v>
+        <v>0.37970276</v>
       </c>
       <c r="N60">
-        <v>0.8270662133333333</v>
+        <v>0.8206305733333332</v>
       </c>
       <c r="O60">
-        <v>0.248119864</v>
+        <v>0.246189172</v>
       </c>
       <c r="P60">
-        <v>0.5789463493333333</v>
+        <v>0.5744414013333332</v>
       </c>
       <c r="Q60">
-        <v>0.6269463493333334</v>
+        <v>0.6224414013333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2462771507452516</v>
+        <v>0.2504209529516437</v>
       </c>
       <c r="T60">
-        <v>1.397815417130496</v>
+        <v>1.42670783997321</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.215748907466946</v>
+        <v>3.161244688696319</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6238,22 +6238,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1291458907101739</v>
+        <v>0.1288307781073422</v>
       </c>
       <c r="C61">
-        <v>7.863510904140536</v>
+        <v>7.814838947906861</v>
       </c>
       <c r="D61">
-        <v>13.63011090414054</v>
+        <v>13.68183894790686</v>
       </c>
       <c r="E61">
-        <v>-2.2064</v>
+        <v>-2.106000000000001</v>
       </c>
       <c r="F61">
-        <v>5.9236</v>
+        <v>6.024</v>
       </c>
       <c r="G61">
         <v>0.157</v>
@@ -6274,28 +6274,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M61">
-        <v>0.37970276</v>
+        <v>0.3861384</v>
       </c>
       <c r="N61">
-        <v>0.8206305733333332</v>
+        <v>0.8141949333333331</v>
       </c>
       <c r="O61">
-        <v>0.246189172</v>
+        <v>0.2442584799999999</v>
       </c>
       <c r="P61">
-        <v>0.5744414013333332</v>
+        <v>0.5699364533333332</v>
       </c>
       <c r="Q61">
-        <v>0.6224414013333333</v>
+        <v>0.6179364533333332</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2504209529516437</v>
+        <v>0.2547719452683555</v>
       </c>
       <c r="T61">
-        <v>1.42670783997321</v>
+        <v>1.457044883958059</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.161244688696319</v>
+        <v>3.108557277218047</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6320,22 +6320,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1288307781073422</v>
+        <v>0.1285156655045105</v>
       </c>
       <c r="C62">
-        <v>7.814838947906861</v>
+        <v>7.766561116737919</v>
       </c>
       <c r="D62">
-        <v>13.68183894790686</v>
+        <v>13.73396111673792</v>
       </c>
       <c r="E62">
-        <v>-2.106000000000001</v>
+        <v>-2.0056</v>
       </c>
       <c r="F62">
-        <v>6.024</v>
+        <v>6.124400000000001</v>
       </c>
       <c r="G62">
         <v>0.157</v>
@@ -6356,28 +6356,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M62">
-        <v>0.3861384</v>
+        <v>0.3925740400000001</v>
       </c>
       <c r="N62">
-        <v>0.8141949333333331</v>
+        <v>0.8077592933333332</v>
       </c>
       <c r="O62">
-        <v>0.2442584799999999</v>
+        <v>0.2423277879999999</v>
       </c>
       <c r="P62">
-        <v>0.5699364533333332</v>
+        <v>0.5654315053333332</v>
       </c>
       <c r="Q62">
-        <v>0.6179364533333332</v>
+        <v>0.6134315053333332</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2547719452683555</v>
+        <v>0.2593460653961807</v>
       </c>
       <c r="T62">
-        <v>1.457044883958059</v>
+        <v>1.488937673788286</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.108557277218047</v>
+        <v>3.057597321853816</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6402,22 +6402,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1285156655045105</v>
+        <v>0.1282005529016787</v>
       </c>
       <c r="C63">
-        <v>7.766561116737919</v>
+        <v>7.718681932221392</v>
       </c>
       <c r="D63">
-        <v>13.73396111673792</v>
+        <v>13.78648193222139</v>
       </c>
       <c r="E63">
-        <v>-2.0056</v>
+        <v>-1.905200000000001</v>
       </c>
       <c r="F63">
-        <v>6.124400000000001</v>
+        <v>6.2248</v>
       </c>
       <c r="G63">
         <v>0.157</v>
@@ -6438,28 +6438,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M63">
-        <v>0.3925740400000001</v>
+        <v>0.39900968</v>
       </c>
       <c r="N63">
-        <v>0.8077592933333332</v>
+        <v>0.8013236533333332</v>
       </c>
       <c r="O63">
-        <v>0.2423277879999999</v>
+        <v>0.2403970959999999</v>
       </c>
       <c r="P63">
-        <v>0.5654315053333332</v>
+        <v>0.5609265573333333</v>
       </c>
       <c r="Q63">
-        <v>0.6134315053333332</v>
+        <v>0.6089265573333333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2593460653961807</v>
+        <v>0.2641609286886282</v>
       </c>
       <c r="T63">
-        <v>1.488937673788286</v>
+        <v>1.522509031504314</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.057597321853816</v>
+        <v>3.008281236017465</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6484,22 +6484,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1282005529016787</v>
+        <v>0.131325240298847</v>
       </c>
       <c r="C64">
-        <v>7.718681932221392</v>
+        <v>7.114589148729955</v>
       </c>
       <c r="D64">
-        <v>13.78648193222139</v>
+        <v>13.28278914872996</v>
       </c>
       <c r="E64">
-        <v>-1.905200000000001</v>
+        <v>-1.8048</v>
       </c>
       <c r="F64">
-        <v>6.2248</v>
+        <v>6.325200000000001</v>
       </c>
       <c r="G64">
         <v>0.157</v>
@@ -6520,45 +6520,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M64">
-        <v>0.39900968</v>
+        <v>0.4547818800000001</v>
       </c>
       <c r="N64">
-        <v>0.8013236533333332</v>
+        <v>0.7455514533333332</v>
       </c>
       <c r="O64">
-        <v>0.2403970959999999</v>
+        <v>0.2236654359999999</v>
       </c>
       <c r="P64">
-        <v>0.5609265573333333</v>
+        <v>0.5218860173333333</v>
       </c>
       <c r="Q64">
-        <v>0.6089265573333333</v>
+        <v>0.5698860173333333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2641609286886282</v>
+        <v>0.2692360548617486</v>
       </c>
       <c r="T64">
-        <v>1.522509031504314</v>
+        <v>1.557895057204992</v>
       </c>
       <c r="U64">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V64">
         <v>0.3</v>
       </c>
       <c r="W64">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.008281236017465</v>
+        <v>2.639360506916707</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6566,22 +6566,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.131325240298847</v>
+        <v>0.1310647276960152</v>
       </c>
       <c r="C65">
-        <v>7.114589148729955</v>
+        <v>7.054772565431147</v>
       </c>
       <c r="D65">
-        <v>13.28278914872996</v>
+        <v>13.32337256543115</v>
       </c>
       <c r="E65">
-        <v>-1.8048</v>
+        <v>-1.7044</v>
       </c>
       <c r="F65">
-        <v>6.325200000000001</v>
+        <v>6.425600000000001</v>
       </c>
       <c r="G65">
         <v>0.157</v>
@@ -6602,28 +6602,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M65">
-        <v>0.4547818800000001</v>
+        <v>0.4620006400000001</v>
       </c>
       <c r="N65">
-        <v>0.7455514533333332</v>
+        <v>0.7383326933333332</v>
       </c>
       <c r="O65">
-        <v>0.2236654359999999</v>
+        <v>0.2214998079999999</v>
       </c>
       <c r="P65">
-        <v>0.5218860173333333</v>
+        <v>0.5168328853333333</v>
       </c>
       <c r="Q65">
-        <v>0.5698860173333333</v>
+        <v>0.5648328853333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2692360548617486</v>
+        <v>0.2745931324889312</v>
       </c>
       <c r="T65">
-        <v>1.557895057204992</v>
+        <v>1.595246973222374</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.639360506916707</v>
+        <v>2.598120498996133</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6648,22 +6648,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1310647276960152</v>
+        <v>0.1308042150931835</v>
       </c>
       <c r="C66">
-        <v>7.054772565431147</v>
+        <v>6.995204734303157</v>
       </c>
       <c r="D66">
-        <v>13.32337256543115</v>
+        <v>13.36420473430316</v>
       </c>
       <c r="E66">
-        <v>-1.7044</v>
+        <v>-1.604</v>
       </c>
       <c r="F66">
-        <v>6.425600000000001</v>
+        <v>6.526000000000001</v>
       </c>
       <c r="G66">
         <v>0.157</v>
@@ -6684,28 +6684,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M66">
-        <v>0.4620006400000001</v>
+        <v>0.4692194000000001</v>
       </c>
       <c r="N66">
-        <v>0.7383326933333332</v>
+        <v>0.7311139333333332</v>
       </c>
       <c r="O66">
-        <v>0.2214998079999999</v>
+        <v>0.21933418</v>
       </c>
       <c r="P66">
-        <v>0.5168328853333333</v>
+        <v>0.5117797533333333</v>
       </c>
       <c r="Q66">
-        <v>0.5648328853333333</v>
+        <v>0.5597797533333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2745931324889312</v>
+        <v>0.2802563288376672</v>
       </c>
       <c r="T66">
-        <v>1.595246973222374</v>
+        <v>1.63473328444075</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.598120498996133</v>
+        <v>2.558149414396193</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6730,22 +6730,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1308042150931835</v>
+        <v>0.1305437024903517</v>
       </c>
       <c r="C67">
-        <v>6.995204734303157</v>
+        <v>6.93588794943063</v>
       </c>
       <c r="D67">
-        <v>13.36420473430316</v>
+        <v>13.40528794943063</v>
       </c>
       <c r="E67">
-        <v>-1.604</v>
+        <v>-1.5036</v>
       </c>
       <c r="F67">
-        <v>6.526000000000001</v>
+        <v>6.626400000000001</v>
       </c>
       <c r="G67">
         <v>0.157</v>
@@ -6766,28 +6766,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M67">
-        <v>0.4692194000000001</v>
+        <v>0.4764381600000001</v>
       </c>
       <c r="N67">
-        <v>0.7311139333333332</v>
+        <v>0.7238951733333332</v>
       </c>
       <c r="O67">
-        <v>0.21933418</v>
+        <v>0.217168552</v>
       </c>
       <c r="P67">
-        <v>0.5117797533333333</v>
+        <v>0.5067266213333332</v>
       </c>
       <c r="Q67">
-        <v>0.5597797533333333</v>
+        <v>0.5547266213333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2802563288376672</v>
+        <v>0.2862526543833875</v>
       </c>
       <c r="T67">
-        <v>1.63473328444075</v>
+        <v>1.676542319848441</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.558149414396193</v>
+        <v>2.51938957478413</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6812,22 +6812,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1305437024903517</v>
+        <v>0.13211228988752</v>
       </c>
       <c r="C68">
-        <v>6.93588794943063</v>
+        <v>6.591868347166681</v>
       </c>
       <c r="D68">
-        <v>13.40528794943063</v>
+        <v>13.16166834716668</v>
       </c>
       <c r="E68">
-        <v>-1.5036</v>
+        <v>-1.4032</v>
       </c>
       <c r="F68">
-        <v>6.626400000000001</v>
+        <v>6.726800000000001</v>
       </c>
       <c r="G68">
         <v>0.157</v>
@@ -6848,45 +6848,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M68">
-        <v>0.4764381600000001</v>
+        <v>0.5098914400000001</v>
       </c>
       <c r="N68">
-        <v>0.7238951733333332</v>
+        <v>0.6904418933333332</v>
       </c>
       <c r="O68">
-        <v>0.217168552</v>
+        <v>0.2071325679999999</v>
       </c>
       <c r="P68">
-        <v>0.5067266213333332</v>
+        <v>0.4833093253333333</v>
       </c>
       <c r="Q68">
-        <v>0.5547266213333333</v>
+        <v>0.5313093253333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2862526543833875</v>
+        <v>0.2926123935985455</v>
       </c>
       <c r="T68">
-        <v>1.676542319848441</v>
+        <v>1.720885236189933</v>
       </c>
       <c r="U68">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V68">
         <v>0.3</v>
       </c>
       <c r="W68">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.51938957478413</v>
+        <v>2.354095870551059</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6894,22 +6894,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.13211228988752</v>
+        <v>0.1318790772846883</v>
       </c>
       <c r="C69">
-        <v>6.591868347166681</v>
+        <v>6.527127034848693</v>
       </c>
       <c r="D69">
-        <v>13.16166834716668</v>
+        <v>13.19732703484869</v>
       </c>
       <c r="E69">
-        <v>-1.4032</v>
+        <v>-1.3028</v>
       </c>
       <c r="F69">
-        <v>6.726800000000001</v>
+        <v>6.827200000000001</v>
       </c>
       <c r="G69">
         <v>0.157</v>
@@ -6930,28 +6930,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M69">
-        <v>0.5098914400000001</v>
+        <v>0.5175017600000001</v>
       </c>
       <c r="N69">
-        <v>0.6904418933333332</v>
+        <v>0.6828315733333331</v>
       </c>
       <c r="O69">
-        <v>0.2071325679999999</v>
+        <v>0.2048494719999999</v>
       </c>
       <c r="P69">
-        <v>0.4833093253333333</v>
+        <v>0.4779821013333332</v>
       </c>
       <c r="Q69">
-        <v>0.5313093253333333</v>
+        <v>0.5259821013333332</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2926123935985455</v>
+        <v>0.2993696165146509</v>
       </c>
       <c r="T69">
-        <v>1.720885236189933</v>
+        <v>1.767999584802768</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.354095870551059</v>
+        <v>2.31947681363119</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6976,22 +6976,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1318790772846883</v>
+        <v>0.1316458646818565</v>
       </c>
       <c r="C70">
-        <v>6.527127034848693</v>
+        <v>6.462579466408733</v>
       </c>
       <c r="D70">
-        <v>13.19732703484869</v>
+        <v>13.23317946640873</v>
       </c>
       <c r="E70">
-        <v>-1.3028</v>
+        <v>-1.2024</v>
       </c>
       <c r="F70">
-        <v>6.827200000000001</v>
+        <v>6.927600000000001</v>
       </c>
       <c r="G70">
         <v>0.157</v>
@@ -7012,28 +7012,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M70">
-        <v>0.5175017600000001</v>
+        <v>0.5251120800000001</v>
       </c>
       <c r="N70">
-        <v>0.6828315733333331</v>
+        <v>0.6752212533333332</v>
       </c>
       <c r="O70">
-        <v>0.2048494719999999</v>
+        <v>0.2025663759999999</v>
       </c>
       <c r="P70">
-        <v>0.4779821013333332</v>
+        <v>0.4726548773333332</v>
       </c>
       <c r="Q70">
-        <v>0.5259821013333332</v>
+        <v>0.5206548773333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2993696165146509</v>
+        <v>0.3065627892963115</v>
       </c>
       <c r="T70">
-        <v>1.767999584802768</v>
+        <v>1.818153568809979</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.31947681363119</v>
+        <v>2.285861207636535</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7058,22 +7058,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1316458646818565</v>
+        <v>0.1314126520790248</v>
       </c>
       <c r="C71">
-        <v>6.462579466408733</v>
+        <v>6.39822722514715</v>
       </c>
       <c r="D71">
-        <v>13.23317946640873</v>
+        <v>13.26922722514715</v>
       </c>
       <c r="E71">
-        <v>-1.2024</v>
+        <v>-1.101999999999999</v>
       </c>
       <c r="F71">
-        <v>6.927600000000001</v>
+        <v>7.028000000000001</v>
       </c>
       <c r="G71">
         <v>0.157</v>
@@ -7094,28 +7094,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M71">
-        <v>0.5251120800000001</v>
+        <v>0.5327224000000002</v>
       </c>
       <c r="N71">
-        <v>0.6752212533333332</v>
+        <v>0.6676109333333331</v>
       </c>
       <c r="O71">
-        <v>0.2025663759999999</v>
+        <v>0.2002832799999999</v>
       </c>
       <c r="P71">
-        <v>0.4726548773333332</v>
+        <v>0.4673276533333331</v>
       </c>
       <c r="Q71">
-        <v>0.5206548773333333</v>
+        <v>0.5153276533333332</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3065627892963115</v>
+        <v>0.3142355069300827</v>
       </c>
       <c r="T71">
-        <v>1.818153568809979</v>
+        <v>1.871651151751004</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.285861207636535</v>
+        <v>2.253206047527442</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7140,22 +7140,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1314126520790248</v>
+        <v>0.1311794394761931</v>
       </c>
       <c r="C72">
-        <v>6.39822722514715</v>
+        <v>6.334071911663334</v>
       </c>
       <c r="D72">
-        <v>13.26922722514715</v>
+        <v>13.30547191166334</v>
       </c>
       <c r="E72">
-        <v>-1.101999999999999</v>
+        <v>-1.001599999999999</v>
       </c>
       <c r="F72">
-        <v>7.028000000000001</v>
+        <v>7.128400000000002</v>
       </c>
       <c r="G72">
         <v>0.157</v>
@@ -7176,28 +7176,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M72">
-        <v>0.5327224000000002</v>
+        <v>0.5403327200000002</v>
       </c>
       <c r="N72">
-        <v>0.6676109333333331</v>
+        <v>0.660000613333333</v>
       </c>
       <c r="O72">
-        <v>0.2002832799999999</v>
+        <v>0.1980001839999999</v>
       </c>
       <c r="P72">
-        <v>0.4673276533333331</v>
+        <v>0.4620004293333331</v>
       </c>
       <c r="Q72">
-        <v>0.5153276533333332</v>
+        <v>0.5100004293333331</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3142355069300827</v>
+        <v>0.3224373775041141</v>
       </c>
       <c r="T72">
-        <v>1.871651151751004</v>
+        <v>1.92883822317072</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.253206047527442</v>
+        <v>2.221470751083393</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7222,22 +7222,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1311794394761931</v>
+        <v>0.1309462268733613</v>
       </c>
       <c r="C73">
-        <v>6.334071911663336</v>
+        <v>6.270115144092634</v>
       </c>
       <c r="D73">
-        <v>13.30547191166334</v>
+        <v>13.34191514409263</v>
       </c>
       <c r="E73">
-        <v>-1.001600000000001</v>
+        <v>-0.9012000000000002</v>
       </c>
       <c r="F73">
-        <v>7.1284</v>
+        <v>7.228800000000001</v>
       </c>
       <c r="G73">
         <v>0.157</v>
@@ -7258,28 +7258,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M73">
-        <v>0.5403327200000001</v>
+        <v>0.54794304</v>
       </c>
       <c r="N73">
-        <v>0.6600006133333332</v>
+        <v>0.6523902933333332</v>
       </c>
       <c r="O73">
-        <v>0.1980001839999999</v>
+        <v>0.195717088</v>
       </c>
       <c r="P73">
-        <v>0.4620004293333332</v>
+        <v>0.4566732053333332</v>
       </c>
       <c r="Q73">
-        <v>0.5100004293333332</v>
+        <v>0.5046732053333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.322437377504114</v>
+        <v>0.3312250959762905</v>
       </c>
       <c r="T73">
-        <v>1.92883822317072</v>
+        <v>1.99011008540613</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.221470751083394</v>
+        <v>2.19061699065168</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7304,22 +7304,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1309462268733613</v>
+        <v>0.1307130142705296</v>
       </c>
       <c r="C74">
-        <v>6.270115144092634</v>
+        <v>6.206358558347139</v>
       </c>
       <c r="D74">
-        <v>13.34191514409263</v>
+        <v>13.37855855834714</v>
       </c>
       <c r="E74">
-        <v>-0.9012000000000002</v>
+        <v>-0.8008000000000006</v>
       </c>
       <c r="F74">
-        <v>7.228800000000001</v>
+        <v>7.3292</v>
       </c>
       <c r="G74">
         <v>0.157</v>
@@ -7340,28 +7340,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M74">
-        <v>0.54794304</v>
+        <v>0.5555533600000001</v>
       </c>
       <c r="N74">
-        <v>0.6523902933333332</v>
+        <v>0.6447799733333331</v>
       </c>
       <c r="O74">
-        <v>0.195717088</v>
+        <v>0.1934339919999999</v>
       </c>
       <c r="P74">
-        <v>0.4566732053333332</v>
+        <v>0.4513459813333332</v>
       </c>
       <c r="Q74">
-        <v>0.5046732053333333</v>
+        <v>0.4993459813333332</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3312250959762905</v>
+        <v>0.340663756557517</v>
       </c>
       <c r="T74">
-        <v>1.99011008540613</v>
+        <v>2.055920604103423</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.19061699065168</v>
+        <v>2.160608538724945</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7386,22 +7386,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1307130142705296</v>
+        <v>0.1304798016676978</v>
       </c>
       <c r="C75">
-        <v>6.206358558347139</v>
+        <v>6.142803808360513</v>
       </c>
       <c r="D75">
-        <v>13.37855855834714</v>
+        <v>13.41540380836051</v>
       </c>
       <c r="E75">
-        <v>-0.8008000000000006</v>
+        <v>-0.7004000000000001</v>
       </c>
       <c r="F75">
-        <v>7.3292</v>
+        <v>7.429600000000001</v>
       </c>
       <c r="G75">
         <v>0.157</v>
@@ -7422,28 +7422,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M75">
-        <v>0.5555533600000001</v>
+        <v>0.5631636800000001</v>
       </c>
       <c r="N75">
-        <v>0.6447799733333331</v>
+        <v>0.6371696533333332</v>
       </c>
       <c r="O75">
-        <v>0.1934339919999999</v>
+        <v>0.191150896</v>
       </c>
       <c r="P75">
-        <v>0.4513459813333332</v>
+        <v>0.4460187573333332</v>
       </c>
       <c r="Q75">
-        <v>0.4993459813333332</v>
+        <v>0.4940187573333333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.340663756557517</v>
+        <v>0.350828467952684</v>
       </c>
       <c r="T75">
-        <v>2.055920604103423</v>
+        <v>2.126793470392815</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.160608538724945</v>
+        <v>2.131411126039472</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7468,22 +7468,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1304798016676978</v>
+        <v>0.1302465890648661</v>
       </c>
       <c r="C76">
-        <v>6.142803808360513</v>
+        <v>6.079452566336794</v>
       </c>
       <c r="D76">
-        <v>13.41540380836051</v>
+        <v>13.4524525663368</v>
       </c>
       <c r="E76">
-        <v>-0.7004000000000001</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="F76">
-        <v>7.429600000000001</v>
+        <v>7.530000000000001</v>
       </c>
       <c r="G76">
         <v>0.157</v>
@@ -7504,28 +7504,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M76">
-        <v>0.5631636800000001</v>
+        <v>0.5707740000000001</v>
       </c>
       <c r="N76">
-        <v>0.6371696533333332</v>
+        <v>0.6295593333333331</v>
       </c>
       <c r="O76">
-        <v>0.191150896</v>
+        <v>0.1888677999999999</v>
       </c>
       <c r="P76">
-        <v>0.4460187573333332</v>
+        <v>0.4406915333333332</v>
       </c>
       <c r="Q76">
-        <v>0.4940187573333333</v>
+        <v>0.4886915333333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.350828467952684</v>
+        <v>0.3618063562594644</v>
       </c>
       <c r="T76">
-        <v>2.126793470392815</v>
+        <v>2.203336165985358</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.131411126039472</v>
+        <v>2.102992311025613</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7550,22 +7550,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1302465890648661</v>
+        <v>0.1300133764620344</v>
       </c>
       <c r="C77">
-        <v>6.079452566336794</v>
+        <v>6.016306523003409</v>
       </c>
       <c r="D77">
-        <v>13.4524525663368</v>
+        <v>13.48970652300341</v>
       </c>
       <c r="E77">
-        <v>-0.5999999999999996</v>
+        <v>-0.4996</v>
       </c>
       <c r="F77">
-        <v>7.530000000000001</v>
+        <v>7.630400000000001</v>
       </c>
       <c r="G77">
         <v>0.157</v>
@@ -7586,28 +7586,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M77">
-        <v>0.5707740000000001</v>
+        <v>0.5783843200000001</v>
       </c>
       <c r="N77">
-        <v>0.6295593333333331</v>
+        <v>0.6219490133333332</v>
       </c>
       <c r="O77">
-        <v>0.1888677999999999</v>
+        <v>0.186584704</v>
       </c>
       <c r="P77">
-        <v>0.4406915333333332</v>
+        <v>0.4353643093333333</v>
       </c>
       <c r="Q77">
-        <v>0.4886915333333333</v>
+        <v>0.4833643093333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3618063562594644</v>
+        <v>0.3736990685918099</v>
       </c>
       <c r="T77">
-        <v>2.203336165985358</v>
+        <v>2.286257419543947</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.102992311025613</v>
+        <v>2.075321359564749</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7632,22 +7632,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1300133764620344</v>
+        <v>0.1297801638592026</v>
       </c>
       <c r="C78">
-        <v>6.016306523003409</v>
+        <v>5.953367387868357</v>
       </c>
       <c r="D78">
-        <v>13.48970652300341</v>
+        <v>13.52716738786836</v>
       </c>
       <c r="E78">
-        <v>-0.4996</v>
+        <v>-0.3991999999999996</v>
       </c>
       <c r="F78">
-        <v>7.630400000000001</v>
+        <v>7.730800000000001</v>
       </c>
       <c r="G78">
         <v>0.157</v>
@@ -7668,28 +7668,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M78">
-        <v>0.5783843200000001</v>
+        <v>0.5859946400000001</v>
       </c>
       <c r="N78">
-        <v>0.6219490133333332</v>
+        <v>0.6143386933333331</v>
       </c>
       <c r="O78">
-        <v>0.186584704</v>
+        <v>0.1843016079999999</v>
       </c>
       <c r="P78">
-        <v>0.4353643093333333</v>
+        <v>0.4300370853333332</v>
       </c>
       <c r="Q78">
-        <v>0.4833643093333333</v>
+        <v>0.4780370853333332</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3736990685918099</v>
+        <v>0.3866259298226201</v>
       </c>
       <c r="T78">
-        <v>2.286257419543947</v>
+        <v>2.376389216890239</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.075321359564749</v>
+        <v>2.048369134115856</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7714,22 +7714,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1297801638592026</v>
+        <v>0.1295469512563709</v>
       </c>
       <c r="C79">
-        <v>5.953367387868357</v>
+        <v>5.890636889481712</v>
       </c>
       <c r="D79">
-        <v>13.52716738786836</v>
+        <v>13.56483688948171</v>
       </c>
       <c r="E79">
-        <v>-0.3991999999999996</v>
+        <v>-0.2988</v>
       </c>
       <c r="F79">
-        <v>7.730800000000001</v>
+        <v>7.831200000000001</v>
       </c>
       <c r="G79">
         <v>0.157</v>
@@ -7750,28 +7750,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M79">
-        <v>0.5859946400000001</v>
+        <v>0.5936049600000001</v>
       </c>
       <c r="N79">
-        <v>0.6143386933333331</v>
+        <v>0.6067283733333332</v>
       </c>
       <c r="O79">
-        <v>0.1843016079999999</v>
+        <v>0.1820185119999999</v>
       </c>
       <c r="P79">
-        <v>0.4300370853333332</v>
+        <v>0.4247098613333332</v>
       </c>
       <c r="Q79">
-        <v>0.4780370853333332</v>
+        <v>0.4727098613333333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3866259298226201</v>
+        <v>0.4007279602562314</v>
       </c>
       <c r="T79">
-        <v>2.376389216890239</v>
+        <v>2.474714813995285</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.048369134115856</v>
+        <v>2.022107991370782</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7796,22 +7796,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1295469512563709</v>
+        <v>0.1371663386535391</v>
       </c>
       <c r="C80">
-        <v>5.890636889481712</v>
+        <v>4.659013413051465</v>
       </c>
       <c r="D80">
-        <v>13.56483688948171</v>
+        <v>12.43361341305147</v>
       </c>
       <c r="E80">
-        <v>-0.2988</v>
+        <v>-0.1983999999999995</v>
       </c>
       <c r="F80">
-        <v>7.831200000000001</v>
+        <v>7.931600000000001</v>
       </c>
       <c r="G80">
         <v>0.157</v>
@@ -7832,45 +7832,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M80">
-        <v>0.5936049600000001</v>
+        <v>0.7138440000000001</v>
       </c>
       <c r="N80">
-        <v>0.6067283733333332</v>
+        <v>0.4864893333333331</v>
       </c>
       <c r="O80">
-        <v>0.1820185119999999</v>
+        <v>0.1459467999999999</v>
       </c>
       <c r="P80">
-        <v>0.4247098613333332</v>
+        <v>0.3405425333333332</v>
       </c>
       <c r="Q80">
-        <v>0.4727098613333333</v>
+        <v>0.3885425333333332</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4007279602562314</v>
+        <v>0.4161730412073293</v>
       </c>
       <c r="T80">
-        <v>2.474714813995285</v>
+        <v>2.582404753681764</v>
       </c>
       <c r="U80">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V80">
         <v>0.3</v>
       </c>
       <c r="W80">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.022107991370782</v>
+        <v>1.681506510292631</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7878,22 +7878,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1371663386535391</v>
+        <v>0.1370325260507074</v>
       </c>
       <c r="C81">
-        <v>4.659013413051465</v>
+        <v>4.576850046908113</v>
       </c>
       <c r="D81">
-        <v>12.43361341305147</v>
+        <v>12.45185004690812</v>
       </c>
       <c r="E81">
-        <v>-0.1983999999999995</v>
+        <v>-0.09799999999999898</v>
       </c>
       <c r="F81">
-        <v>7.931600000000001</v>
+        <v>8.032000000000002</v>
       </c>
       <c r="G81">
         <v>0.157</v>
@@ -7914,28 +7914,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M81">
-        <v>0.7138440000000001</v>
+        <v>0.7228800000000002</v>
       </c>
       <c r="N81">
-        <v>0.4864893333333331</v>
+        <v>0.4774533333333331</v>
       </c>
       <c r="O81">
-        <v>0.1459467999999999</v>
+        <v>0.1432359999999999</v>
       </c>
       <c r="P81">
-        <v>0.3405425333333332</v>
+        <v>0.3342173333333331</v>
       </c>
       <c r="Q81">
-        <v>0.3885425333333332</v>
+        <v>0.3822173333333332</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4161730412073293</v>
+        <v>0.4331626302535371</v>
       </c>
       <c r="T81">
-        <v>2.582404753681764</v>
+        <v>2.700863687336891</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.681506510292631</v>
+        <v>1.660487678913973</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7960,22 +7960,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1370325260507074</v>
+        <v>0.1368987134478757</v>
       </c>
       <c r="C82">
-        <v>4.576850046908113</v>
+        <v>4.494740255427912</v>
       </c>
       <c r="D82">
-        <v>12.45185004690812</v>
+        <v>12.47014025542791</v>
       </c>
       <c r="E82">
-        <v>-0.09799999999999898</v>
+        <v>0.002399999999999736</v>
       </c>
       <c r="F82">
-        <v>8.032000000000002</v>
+        <v>8.132400000000001</v>
       </c>
       <c r="G82">
         <v>0.157</v>
@@ -7996,28 +7996,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M82">
-        <v>0.7228800000000002</v>
+        <v>0.731916</v>
       </c>
       <c r="N82">
-        <v>0.4774533333333331</v>
+        <v>0.4684173333333332</v>
       </c>
       <c r="O82">
-        <v>0.1432359999999999</v>
+        <v>0.1405252</v>
       </c>
       <c r="P82">
-        <v>0.3342173333333331</v>
+        <v>0.3278921333333333</v>
       </c>
       <c r="Q82">
-        <v>0.3822173333333332</v>
+        <v>0.3758921333333333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4331626302535371</v>
+        <v>0.4519405970940826</v>
       </c>
       <c r="T82">
-        <v>2.700863687336891</v>
+        <v>2.8317919824294</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.660487678913973</v>
+        <v>1.639987831026147</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8042,22 +8042,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1368987134478757</v>
+        <v>0.1367649008450439</v>
       </c>
       <c r="C83">
-        <v>4.494740255427912</v>
+        <v>4.412684275041569</v>
       </c>
       <c r="D83">
-        <v>12.47014025542791</v>
+        <v>12.48848427504157</v>
       </c>
       <c r="E83">
-        <v>0.002399999999999736</v>
+        <v>0.1028000000000002</v>
       </c>
       <c r="F83">
-        <v>8.132400000000001</v>
+        <v>8.232800000000001</v>
       </c>
       <c r="G83">
         <v>0.157</v>
@@ -8078,28 +8078,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M83">
-        <v>0.731916</v>
+        <v>0.7409520000000001</v>
       </c>
       <c r="N83">
-        <v>0.4684173333333332</v>
+        <v>0.4593813333333332</v>
       </c>
       <c r="O83">
-        <v>0.1405252</v>
+        <v>0.1378143999999999</v>
       </c>
       <c r="P83">
-        <v>0.3278921333333333</v>
+        <v>0.3215669333333332</v>
       </c>
       <c r="Q83">
-        <v>0.3758921333333333</v>
+        <v>0.3695669333333333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4519405970940826</v>
+        <v>0.4728050046946886</v>
       </c>
       <c r="T83">
-        <v>2.8317919824294</v>
+        <v>2.977267865865521</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.639987831026147</v>
+        <v>1.619987979428267</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8124,22 +8124,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1367649008450439</v>
+        <v>0.1366310882422122</v>
       </c>
       <c r="C84">
-        <v>4.412684275041569</v>
+        <v>4.330682343573026</v>
       </c>
       <c r="D84">
-        <v>12.48848427504157</v>
+        <v>12.50688234357303</v>
       </c>
       <c r="E84">
-        <v>0.1028000000000002</v>
+        <v>0.2032000000000007</v>
       </c>
       <c r="F84">
-        <v>8.232800000000001</v>
+        <v>8.333200000000001</v>
       </c>
       <c r="G84">
         <v>0.157</v>
@@ -8160,28 +8160,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M84">
-        <v>0.7409520000000001</v>
+        <v>0.7499880000000001</v>
       </c>
       <c r="N84">
-        <v>0.4593813333333332</v>
+        <v>0.4503453333333332</v>
       </c>
       <c r="O84">
-        <v>0.1378143999999999</v>
+        <v>0.1351035999999999</v>
       </c>
       <c r="P84">
-        <v>0.3215669333333332</v>
+        <v>0.3152417333333332</v>
       </c>
       <c r="Q84">
-        <v>0.3695669333333333</v>
+        <v>0.3632417333333333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4728050046946886</v>
+        <v>0.4961240484836012</v>
       </c>
       <c r="T84">
-        <v>2.977267865865521</v>
+        <v>3.139858559117656</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.619987979428267</v>
+        <v>1.600470051965276</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8206,22 +8206,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1366310882422122</v>
+        <v>0.1364972756393805</v>
       </c>
       <c r="C85">
-        <v>4.330682343573026</v>
+        <v>4.248734700249727</v>
       </c>
       <c r="D85">
-        <v>12.50688234357303</v>
+        <v>12.52533470024973</v>
       </c>
       <c r="E85">
-        <v>0.2032000000000007</v>
+        <v>0.3036000000000012</v>
       </c>
       <c r="F85">
-        <v>8.333200000000001</v>
+        <v>8.433600000000002</v>
       </c>
       <c r="G85">
         <v>0.157</v>
@@ -8242,28 +8242,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M85">
-        <v>0.7499880000000001</v>
+        <v>0.7590240000000001</v>
       </c>
       <c r="N85">
-        <v>0.4503453333333332</v>
+        <v>0.4413093333333331</v>
       </c>
       <c r="O85">
-        <v>0.1351035999999999</v>
+        <v>0.1323927999999999</v>
       </c>
       <c r="P85">
-        <v>0.3152417333333332</v>
+        <v>0.3089165333333332</v>
       </c>
       <c r="Q85">
-        <v>0.3632417333333333</v>
+        <v>0.3569165333333332</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4961240484836012</v>
+        <v>0.5223579727461281</v>
       </c>
       <c r="T85">
-        <v>3.139858559117656</v>
+        <v>3.322773089026308</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.600470051965276</v>
+        <v>1.581416837060927</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8288,22 +8288,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1364972756393805</v>
+        <v>0.1363634630365487</v>
       </c>
       <c r="C86">
-        <v>4.248734700249729</v>
+        <v>4.166841585713051</v>
       </c>
       <c r="D86">
-        <v>12.52533470024973</v>
+        <v>12.54384158571305</v>
       </c>
       <c r="E86">
-        <v>0.3035999999999994</v>
+        <v>0.4039999999999999</v>
       </c>
       <c r="F86">
-        <v>8.4336</v>
+        <v>8.534000000000001</v>
       </c>
       <c r="G86">
         <v>0.157</v>
@@ -8324,28 +8324,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M86">
-        <v>0.759024</v>
+        <v>0.7680600000000001</v>
       </c>
       <c r="N86">
-        <v>0.4413093333333332</v>
+        <v>0.4322733333333332</v>
       </c>
       <c r="O86">
-        <v>0.1323927999999999</v>
+        <v>0.1296819999999999</v>
       </c>
       <c r="P86">
-        <v>0.3089165333333332</v>
+        <v>0.3025913333333332</v>
       </c>
       <c r="Q86">
-        <v>0.3569165333333333</v>
+        <v>0.3505913333333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5223579727461277</v>
+        <v>0.5520897535769913</v>
       </c>
       <c r="T86">
-        <v>3.322773089026306</v>
+        <v>3.530076222922778</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.581416837060927</v>
+        <v>1.562811933095504</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8370,22 +8370,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1363634630365487</v>
+        <v>0.136229650433717</v>
       </c>
       <c r="C87">
-        <v>4.166841585713051</v>
+        <v>4.085003242028685</v>
       </c>
       <c r="D87">
-        <v>12.54384158571305</v>
+        <v>12.56240324202869</v>
       </c>
       <c r="E87">
-        <v>0.4039999999999999</v>
+        <v>0.5044000000000004</v>
       </c>
       <c r="F87">
-        <v>8.534000000000001</v>
+        <v>8.634400000000001</v>
       </c>
       <c r="G87">
         <v>0.157</v>
@@ -8406,28 +8406,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M87">
-        <v>0.7680600000000001</v>
+        <v>0.7770960000000001</v>
       </c>
       <c r="N87">
-        <v>0.4322733333333332</v>
+        <v>0.4232373333333331</v>
       </c>
       <c r="O87">
-        <v>0.1296819999999999</v>
+        <v>0.1269711999999999</v>
       </c>
       <c r="P87">
-        <v>0.3025913333333332</v>
+        <v>0.2962661333333332</v>
       </c>
       <c r="Q87">
-        <v>0.3505913333333333</v>
+        <v>0.3442661333333332</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5520897535769913</v>
+        <v>0.5860689316694068</v>
       </c>
       <c r="T87">
-        <v>3.530076222922778</v>
+        <v>3.766994090233031</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.562811933095504</v>
+        <v>1.544639701315324</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8452,22 +8452,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.136229650433717</v>
+        <v>0.1360958378308852</v>
       </c>
       <c r="C88">
-        <v>4.085003242028685</v>
+        <v>4.003219912697229</v>
       </c>
       <c r="D88">
-        <v>12.56240324202869</v>
+        <v>12.58101991269723</v>
       </c>
       <c r="E88">
-        <v>0.5044000000000004</v>
+        <v>0.6047999999999991</v>
       </c>
       <c r="F88">
-        <v>8.634400000000001</v>
+        <v>8.7348</v>
       </c>
       <c r="G88">
         <v>0.157</v>
@@ -8488,28 +8488,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M88">
-        <v>0.7770960000000001</v>
+        <v>0.7861319999999999</v>
       </c>
       <c r="N88">
-        <v>0.4232373333333331</v>
+        <v>0.4142013333333333</v>
       </c>
       <c r="O88">
-        <v>0.1269711999999999</v>
+        <v>0.1242604</v>
       </c>
       <c r="P88">
-        <v>0.2962661333333332</v>
+        <v>0.2899409333333333</v>
       </c>
       <c r="Q88">
-        <v>0.3442661333333332</v>
+        <v>0.3379409333333334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5860689316694068</v>
+        <v>0.625275675622194</v>
       </c>
       <c r="T88">
-        <v>3.766994090233031</v>
+        <v>4.040360860206401</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.544639701315324</v>
+        <v>1.526885221989861</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8534,22 +8534,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1360958378308852</v>
+        <v>0.1359620252280535</v>
       </c>
       <c r="C89">
-        <v>4.003219912697229</v>
+        <v>3.921491842664832</v>
       </c>
       <c r="D89">
-        <v>12.58101991269723</v>
+        <v>12.59969184266483</v>
       </c>
       <c r="E89">
-        <v>0.6047999999999991</v>
+        <v>0.7051999999999996</v>
       </c>
       <c r="F89">
-        <v>8.7348</v>
+        <v>8.8352</v>
       </c>
       <c r="G89">
         <v>0.157</v>
@@ -8570,28 +8570,28 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M89">
-        <v>0.7861319999999999</v>
+        <v>0.795168</v>
       </c>
       <c r="N89">
-        <v>0.4142013333333333</v>
+        <v>0.4051653333333333</v>
       </c>
       <c r="O89">
-        <v>0.1242604</v>
+        <v>0.1215496</v>
       </c>
       <c r="P89">
-        <v>0.2899409333333333</v>
+        <v>0.2836157333333333</v>
       </c>
       <c r="Q89">
-        <v>0.3379409333333334</v>
+        <v>0.3316157333333333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.625275675622194</v>
+        <v>0.6710168769004458</v>
       </c>
       <c r="T89">
-        <v>4.040360860206401</v>
+        <v>4.359288758508666</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.526885221989861</v>
+        <v>1.509534253558158</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8616,22 +8616,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1359620252280535</v>
+        <v>0.1768553735378904</v>
       </c>
       <c r="C90">
-        <v>3.921491842664832</v>
+        <v>-0.1104034727083842</v>
       </c>
       <c r="D90">
-        <v>12.59969184266483</v>
+        <v>8.668196527291617</v>
       </c>
       <c r="E90">
-        <v>0.7051999999999996</v>
+        <v>0.8056000000000001</v>
       </c>
       <c r="F90">
-        <v>8.8352</v>
+        <v>8.935600000000001</v>
       </c>
       <c r="G90">
         <v>0.157</v>
@@ -8652,45 +8652,45 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M90">
-        <v>0.795168</v>
+        <v>1.31174608</v>
       </c>
       <c r="N90">
-        <v>0.4051653333333333</v>
+        <v>-0.111412746666667</v>
       </c>
       <c r="O90">
-        <v>0.1215496</v>
+        <v>-0.0334238240000001</v>
       </c>
       <c r="P90">
-        <v>0.2836157333333333</v>
+        <v>-0.0779889226666669</v>
       </c>
       <c r="Q90">
-        <v>0.3316157333333333</v>
+        <v>-0.02998892266666686</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6710168769004458</v>
+        <v>0.746090067294838</v>
       </c>
       <c r="T90">
-        <v>4.359288758508666</v>
+        <v>4.882732265942592</v>
       </c>
       <c r="U90">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.3</v>
+        <v>0.2745195929992792</v>
       </c>
       <c r="W90">
-        <v>0.063</v>
+        <v>0.1065005237477058</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>1.509534253558158</v>
+        <v>0.9150653099975973</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8698,22 +8698,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1768553735378904</v>
+        <v>0.1778653735378903</v>
       </c>
       <c r="C91">
-        <v>-0.1104034727083842</v>
+        <v>-0.2770954783873201</v>
       </c>
       <c r="D91">
-        <v>8.668196527291617</v>
+        <v>8.601904521612681</v>
       </c>
       <c r="E91">
-        <v>0.8056000000000001</v>
+        <v>0.9060000000000006</v>
       </c>
       <c r="F91">
-        <v>8.935600000000001</v>
+        <v>9.036000000000001</v>
       </c>
       <c r="G91">
         <v>0.157</v>
@@ -8734,37 +8734,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M91">
-        <v>1.31174608</v>
+        <v>1.3264848</v>
       </c>
       <c r="N91">
-        <v>-0.111412746666667</v>
+        <v>-0.126151466666667</v>
       </c>
       <c r="O91">
-        <v>-0.0334238240000001</v>
+        <v>-0.0378454400000001</v>
       </c>
       <c r="P91">
-        <v>-0.0779889226666669</v>
+        <v>-0.0883060266666669</v>
       </c>
       <c r="Q91">
-        <v>-0.02998892266666686</v>
+        <v>-0.04030602666666686</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.746090067294838</v>
+        <v>0.8161190740243218</v>
       </c>
       <c r="T91">
-        <v>4.882732265942592</v>
+        <v>5.371005492536852</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2745195929992792</v>
+        <v>0.2714693752992872</v>
       </c>
       <c r="W91">
-        <v>0.1065005237477058</v>
+        <v>0.1069482957060646</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9150653099975973</v>
+        <v>0.9048979176642906</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8780,22 +8780,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1778653735378903</v>
+        <v>0.1788753735378903</v>
       </c>
       <c r="C92">
-        <v>-0.2770954783873201</v>
+        <v>-0.442781213349809</v>
       </c>
       <c r="D92">
-        <v>8.601904521612681</v>
+        <v>8.536618786650193</v>
       </c>
       <c r="E92">
-        <v>0.9060000000000006</v>
+        <v>1.006400000000001</v>
       </c>
       <c r="F92">
-        <v>9.036000000000001</v>
+        <v>9.136400000000002</v>
       </c>
       <c r="G92">
         <v>0.157</v>
@@ -8816,37 +8816,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M92">
-        <v>1.3264848</v>
+        <v>1.34122352</v>
       </c>
       <c r="N92">
-        <v>-0.126151466666667</v>
+        <v>-0.1408901866666672</v>
       </c>
       <c r="O92">
-        <v>-0.0378454400000001</v>
+        <v>-0.04226705600000016</v>
       </c>
       <c r="P92">
-        <v>-0.0883060266666669</v>
+        <v>-0.09862313066666703</v>
       </c>
       <c r="Q92">
-        <v>-0.04030602666666686</v>
+        <v>-0.05062313066666699</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8161190740243218</v>
+        <v>0.9017100822492465</v>
       </c>
       <c r="T92">
-        <v>5.371005492536852</v>
+        <v>5.967783880596503</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2714693752992872</v>
+        <v>0.2684861953509433</v>
       </c>
       <c r="W92">
-        <v>0.1069482957060646</v>
+        <v>0.1073862265224815</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9048979176642906</v>
+        <v>0.8949539845031445</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8862,22 +8862,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1788753735378903</v>
+        <v>0.1798853735378904</v>
       </c>
       <c r="C93">
-        <v>-0.442781213349809</v>
+        <v>-0.6074834168416778</v>
       </c>
       <c r="D93">
-        <v>8.536618786650193</v>
+        <v>8.472316583158323</v>
       </c>
       <c r="E93">
-        <v>1.006400000000001</v>
+        <v>1.1068</v>
       </c>
       <c r="F93">
-        <v>9.136400000000002</v>
+        <v>9.236800000000001</v>
       </c>
       <c r="G93">
         <v>0.157</v>
@@ -8898,37 +8898,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M93">
-        <v>1.34122352</v>
+        <v>1.35596224</v>
       </c>
       <c r="N93">
-        <v>-0.1408901866666672</v>
+        <v>-0.155628906666667</v>
       </c>
       <c r="O93">
-        <v>-0.04226705600000016</v>
+        <v>-0.04668867200000008</v>
       </c>
       <c r="P93">
-        <v>-0.09862313066666703</v>
+        <v>-0.1089402346666669</v>
       </c>
       <c r="Q93">
-        <v>-0.05062313066666699</v>
+        <v>-0.06094023466666683</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9017100822492465</v>
+        <v>1.008698842530403</v>
       </c>
       <c r="T93">
-        <v>5.967783880596503</v>
+        <v>6.713756865671067</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2684861953509433</v>
+        <v>0.265567867140607</v>
       </c>
       <c r="W93">
-        <v>0.1073862265224815</v>
+        <v>0.1078146371037589</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8949539845031445</v>
+        <v>0.8852262238020234</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8944,22 +8944,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1798853735378904</v>
+        <v>0.1808953735378904</v>
       </c>
       <c r="C94">
-        <v>-0.6074834168416778</v>
+        <v>-0.771224148096179</v>
       </c>
       <c r="D94">
-        <v>8.472316583158323</v>
+        <v>8.408975851903822</v>
       </c>
       <c r="E94">
-        <v>1.1068</v>
+        <v>1.2072</v>
       </c>
       <c r="F94">
-        <v>9.236800000000001</v>
+        <v>9.337200000000001</v>
       </c>
       <c r="G94">
         <v>0.157</v>
@@ -8980,37 +8980,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M94">
-        <v>1.35596224</v>
+        <v>1.37070096</v>
       </c>
       <c r="N94">
-        <v>-0.155628906666667</v>
+        <v>-0.1703676266666669</v>
       </c>
       <c r="O94">
-        <v>-0.04668867200000008</v>
+        <v>-0.05111028800000008</v>
       </c>
       <c r="P94">
-        <v>-0.1089402346666669</v>
+        <v>-0.1192573386666669</v>
       </c>
       <c r="Q94">
-        <v>-0.06094023466666683</v>
+        <v>-0.07125733866666681</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.008698842530403</v>
+        <v>1.146255820034746</v>
       </c>
       <c r="T94">
-        <v>6.713756865671067</v>
+        <v>7.672864989338364</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.265567867140607</v>
+        <v>0.2627122986767295</v>
       </c>
       <c r="W94">
-        <v>0.1078146371037589</v>
+        <v>0.1082338345542561</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8852262238020234</v>
+        <v>0.8757076622557651</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9026,22 +9026,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1808953735378904</v>
+        <v>0.1819053735378904</v>
       </c>
       <c r="C95">
-        <v>-0.771224148096179</v>
+        <v>-0.934024811564905</v>
       </c>
       <c r="D95">
-        <v>8.408975851903822</v>
+        <v>8.346575188435096</v>
       </c>
       <c r="E95">
-        <v>1.2072</v>
+        <v>1.307600000000001</v>
       </c>
       <c r="F95">
-        <v>9.337200000000001</v>
+        <v>9.437600000000002</v>
       </c>
       <c r="G95">
         <v>0.157</v>
@@ -9062,37 +9062,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M95">
-        <v>1.37070096</v>
+        <v>1.38543968</v>
       </c>
       <c r="N95">
-        <v>-0.1703676266666669</v>
+        <v>-0.1851063466666671</v>
       </c>
       <c r="O95">
-        <v>-0.05111028800000008</v>
+        <v>-0.05553190400000014</v>
       </c>
       <c r="P95">
-        <v>-0.1192573386666669</v>
+        <v>-0.129574442666667</v>
       </c>
       <c r="Q95">
-        <v>-0.07125733866666681</v>
+        <v>-0.08157444266666697</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.146255820034746</v>
+        <v>1.329665123373871</v>
       </c>
       <c r="T95">
-        <v>7.672864989338364</v>
+        <v>8.95167582089476</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2627122986767295</v>
+        <v>0.2599174869886792</v>
       </c>
       <c r="W95">
-        <v>0.1082338345542561</v>
+        <v>0.1086441129100619</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8757076622557651</v>
+        <v>0.8663916232955973</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9108,22 +9108,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1819053735378904</v>
+        <v>0.1829153735378904</v>
       </c>
       <c r="C96">
-        <v>-0.934024811564905</v>
+        <v>-1.095906181033586</v>
       </c>
       <c r="D96">
-        <v>8.346575188435096</v>
+        <v>8.285093818966416</v>
       </c>
       <c r="E96">
-        <v>1.307600000000001</v>
+        <v>1.408000000000001</v>
       </c>
       <c r="F96">
-        <v>9.437600000000002</v>
+        <v>9.538000000000002</v>
       </c>
       <c r="G96">
         <v>0.157</v>
@@ -9144,37 +9144,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M96">
-        <v>1.38543968</v>
+        <v>1.4001784</v>
       </c>
       <c r="N96">
-        <v>-0.1851063466666671</v>
+        <v>-0.1998450666666671</v>
       </c>
       <c r="O96">
-        <v>-0.05553190400000014</v>
+        <v>-0.05995352000000014</v>
       </c>
       <c r="P96">
-        <v>-0.129574442666667</v>
+        <v>-0.139891546666667</v>
       </c>
       <c r="Q96">
-        <v>-0.08157444266666697</v>
+        <v>-0.09189154666666693</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.329665123373871</v>
+        <v>1.586438148048646</v>
       </c>
       <c r="T96">
-        <v>8.95167582089476</v>
+        <v>10.74201098507372</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2599174869886792</v>
+        <v>0.2571815134414299</v>
       </c>
       <c r="W96">
-        <v>0.1086441129100619</v>
+        <v>0.1090457538267981</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8663916232955973</v>
+        <v>0.8572717114714332</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9190,22 +9190,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1829153735378904</v>
+        <v>0.1839253735378903</v>
       </c>
       <c r="C97">
-        <v>-1.095906181033586</v>
+        <v>-1.256888422679873</v>
       </c>
       <c r="D97">
-        <v>8.285093818966416</v>
+        <v>8.224511577320129</v>
       </c>
       <c r="E97">
-        <v>1.408000000000001</v>
+        <v>1.508400000000002</v>
       </c>
       <c r="F97">
-        <v>9.538000000000002</v>
+        <v>9.638400000000003</v>
       </c>
       <c r="G97">
         <v>0.157</v>
@@ -9226,37 +9226,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M97">
-        <v>1.4001784</v>
+        <v>1.414917120000001</v>
       </c>
       <c r="N97">
-        <v>-0.1998450666666671</v>
+        <v>-0.2145837866666673</v>
       </c>
       <c r="O97">
-        <v>-0.05995352000000014</v>
+        <v>-0.06437513600000019</v>
       </c>
       <c r="P97">
-        <v>-0.139891546666667</v>
+        <v>-0.1502086506666671</v>
       </c>
       <c r="Q97">
-        <v>-0.09189154666666693</v>
+        <v>-0.1022086506666671</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.586438148048646</v>
+        <v>1.971597685060808</v>
       </c>
       <c r="T97">
-        <v>10.74201098507372</v>
+        <v>13.42751373134215</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2571815134414299</v>
+        <v>0.2545025393430817</v>
       </c>
       <c r="W97">
-        <v>0.1090457538267981</v>
+        <v>0.1094390272244356</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8572717114714332</v>
+        <v>0.8483417978102723</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9272,22 +9272,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1839253735378903</v>
+        <v>0.1849353735378904</v>
       </c>
       <c r="C98">
-        <v>-1.256888422679872</v>
+        <v>-1.416991117126811</v>
       </c>
       <c r="D98">
-        <v>8.224511577320129</v>
+        <v>8.16480888287319</v>
       </c>
       <c r="E98">
-        <v>1.5084</v>
+        <v>1.6088</v>
       </c>
       <c r="F98">
-        <v>9.638400000000001</v>
+        <v>9.738800000000001</v>
       </c>
       <c r="G98">
         <v>0.157</v>
@@ -9308,37 +9308,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M98">
-        <v>1.41491712</v>
+        <v>1.42965584</v>
       </c>
       <c r="N98">
-        <v>-0.2145837866666669</v>
+        <v>-0.2293225066666671</v>
       </c>
       <c r="O98">
-        <v>-0.06437513600000007</v>
+        <v>-0.06879675200000013</v>
       </c>
       <c r="P98">
-        <v>-0.1502086506666668</v>
+        <v>-0.160525754666667</v>
       </c>
       <c r="Q98">
-        <v>-0.1022086506666668</v>
+        <v>-0.1125257546666669</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.971597685060803</v>
+        <v>2.613530246747737</v>
       </c>
       <c r="T98">
-        <v>13.42751373134212</v>
+        <v>17.90335164178949</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2545025393430818</v>
+        <v>0.2518788018240809</v>
       </c>
       <c r="W98">
-        <v>0.1094390272244356</v>
+        <v>0.1098241918922249</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8483417978102725</v>
+        <v>0.8395960060802696</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9354,22 +9354,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1849353735378904</v>
+        <v>0.1859453735378903</v>
       </c>
       <c r="C99">
-        <v>-1.416991117126811</v>
+        <v>-1.576233280542729</v>
       </c>
       <c r="D99">
-        <v>8.16480888287319</v>
+        <v>8.105966719457271</v>
       </c>
       <c r="E99">
-        <v>1.6088</v>
+        <v>1.709199999999999</v>
       </c>
       <c r="F99">
-        <v>9.738800000000001</v>
+        <v>9.8392</v>
       </c>
       <c r="G99">
         <v>0.157</v>
@@ -9390,37 +9390,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M99">
-        <v>1.42965584</v>
+        <v>1.44439456</v>
       </c>
       <c r="N99">
-        <v>-0.2293225066666671</v>
+        <v>-0.2440612266666669</v>
       </c>
       <c r="O99">
-        <v>-0.06879675200000013</v>
+        <v>-0.07321836800000005</v>
       </c>
       <c r="P99">
-        <v>-0.160525754666667</v>
+        <v>-0.1708428586666668</v>
       </c>
       <c r="Q99">
-        <v>-0.1125257546666669</v>
+        <v>-0.1228428586666668</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.613530246747737</v>
+        <v>3.897395370121604</v>
       </c>
       <c r="T99">
-        <v>17.90335164178949</v>
+        <v>26.85502746268423</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2518788018240809</v>
+        <v>0.2493086099687332</v>
       </c>
       <c r="W99">
-        <v>0.1098241918922249</v>
+        <v>0.11020149605659</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8395960060802696</v>
+        <v>0.8310286998957772</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9436,22 +9436,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1859453735378903</v>
+        <v>0.1869553735378904</v>
       </c>
       <c r="C100">
-        <v>-1.576233280542729</v>
+        <v>-1.734633384835284</v>
       </c>
       <c r="D100">
-        <v>8.105966719457271</v>
+        <v>8.047966615164716</v>
       </c>
       <c r="E100">
-        <v>1.709199999999999</v>
+        <v>1.8096</v>
       </c>
       <c r="F100">
-        <v>9.8392</v>
+        <v>9.9396</v>
       </c>
       <c r="G100">
         <v>0.157</v>
@@ -9472,37 +9472,37 @@
         <v>1.200333333333333</v>
       </c>
       <c r="M100">
-        <v>1.44439456</v>
+        <v>1.45913328</v>
       </c>
       <c r="N100">
-        <v>-0.2440612266666669</v>
+        <v>-0.2587999466666671</v>
       </c>
       <c r="O100">
-        <v>-0.07321836800000005</v>
+        <v>-0.07763998400000012</v>
       </c>
       <c r="P100">
-        <v>-0.1708428586666668</v>
+        <v>-0.181159962666667</v>
       </c>
       <c r="Q100">
-        <v>-0.1228428586666668</v>
+        <v>-0.1331599626666669</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.897395370121604</v>
+        <v>7.748990740243211</v>
       </c>
       <c r="T100">
-        <v>26.85502746268423</v>
+        <v>53.71005492536847</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2493086099687332</v>
+        <v>0.2467903411811702</v>
       </c>
       <c r="W100">
-        <v>0.11020149605659</v>
+        <v>0.1105711779146042</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9510,91 +9510,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8310286998957772</v>
+        <v>0.8226344706039006</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1869553735378904</v>
-      </c>
-      <c r="C101">
-        <v>-1.734633384835284</v>
-      </c>
-      <c r="D101">
-        <v>8.047966615164716</v>
-      </c>
-      <c r="E101">
-        <v>1.8096</v>
-      </c>
-      <c r="F101">
-        <v>9.9396</v>
-      </c>
-      <c r="G101">
-        <v>0.157</v>
-      </c>
-      <c r="H101">
-        <v>1.91</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.248333333333333</v>
-      </c>
-      <c r="K101">
-        <v>0.04800000000000004</v>
-      </c>
-      <c r="L101">
-        <v>1.200333333333333</v>
-      </c>
-      <c r="M101">
-        <v>1.45913328</v>
-      </c>
-      <c r="N101">
-        <v>-0.2587999466666671</v>
-      </c>
-      <c r="O101">
-        <v>-0.07763998400000012</v>
-      </c>
-      <c r="P101">
-        <v>-0.181159962666667</v>
-      </c>
-      <c r="Q101">
-        <v>-0.1331599626666669</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.748990740243211</v>
-      </c>
-      <c r="T101">
-        <v>53.71005492536847</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2467903411811702</v>
-      </c>
-      <c r="W101">
-        <v>0.1105711779146042</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8226344706039006</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
